--- a/trading_signals/risk_management/risk_workbook_20260606_031417.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260606_031417.xlsx
@@ -175,19 +175,19 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -728,7 +728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-05  ·  Generated 2026-06-06T03:15:09  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-05  ·  Generated 2026-06-10T09:47:46  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1007417.25</v>
+        <v>1007255.64</v>
       </c>
     </row>
     <row r="5">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>2.516</v>
+        <v>2.517</v>
       </c>
     </row>
     <row r="6">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.7302999999999999</v>
+        <v>0.7292999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>8.84</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="14">
@@ -840,7 +840,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>2.72 / 1.36</t>
+          <t>2.69 / 1.35</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>2.516</v>
+        <v>2.517</v>
       </c>
     </row>
     <row r="16">
@@ -862,7 +862,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>BWA (34.01% NAV)</t>
+          <t>BWA (34.02% NAV)</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       <c r="B13" s="13" t="n">
         <v>5558.93</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>13.34</v>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       <c r="B15" s="13" t="n">
         <v>3082.96</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>7.4</v>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       <c r="B17" s="13" t="n">
         <v>2820.38</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>6.77</v>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       <c r="B19" s="13" t="n">
         <v>2644.94</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>6.35</v>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       <c r="B21" s="13" t="n">
         <v>2213.83</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="17" t="n">
         <v>5.31</v>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       <c r="B23" s="13" t="n">
         <v>1767.25</v>
       </c>
-      <c r="C23" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>4.24</v>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       <c r="B25" s="13" t="n">
         <v>134.56</v>
       </c>
-      <c r="C25" s="16" t="n">
+      <c r="C25" s="17" t="n">
         <v>0.32</v>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
           <t>PFE</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>HAS/PFE</t>
         </is>
@@ -1306,7 +1306,7 @@
       <c r="D7" s="13" t="n">
         <v>34993203</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1337,18 +1337,18 @@
           <t>REGN</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>KLAC/REGN</t>
         </is>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="15" t="n">
         <v>23</v>
       </c>
       <c r="D9" s="13" t="n">
         <v>1046958</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>KLAC/LOW</t>
         </is>
@@ -1390,7 +1390,7 @@
       <c r="D11" s="13" t="n">
         <v>3133808</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
           <t>VLTO</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>FFIV/VLTO</t>
         </is>
@@ -1432,7 +1432,7 @@
       <c r="D13" s="13" t="n">
         <v>2497435</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
           <t>BSX</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>LRCX/BSX</t>
         </is>
@@ -1474,7 +1474,7 @@
       <c r="D15" s="13" t="n">
         <v>18787644</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
           <t>RMD</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>LRCX/RMD</t>
         </is>
@@ -1516,7 +1516,7 @@
       <c r="D17" s="13" t="n">
         <v>1551466</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
           <t>CAG</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>CSCO/CAG</t>
         </is>
@@ -1558,7 +1558,7 @@
       <c r="D19" s="13" t="n">
         <v>14568435</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1635,8 +1635,8 @@
           <t>SPY -5%</t>
         </is>
       </c>
-      <c r="B4" s="18" t="n">
-        <v>-95352.03999999999</v>
+      <c r="B4" s="19" t="n">
+        <v>-95336.75</v>
       </c>
       <c r="C4" s="22" t="n">
         <v>-9.470000000000001</v>
@@ -1648,8 +1648,8 @@
           <t>SPY -10%</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n">
-        <v>-190704.09</v>
+      <c r="B5" s="18" t="n">
+        <v>-190673.49</v>
       </c>
       <c r="C5" s="20" t="n">
         <v>-18.93</v>
@@ -1661,8 +1661,8 @@
           <t>VIX +10pt</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
-        <v>-95352.03999999999</v>
+      <c r="B6" s="19" t="n">
+        <v>-95336.75</v>
       </c>
       <c r="C6" s="22" t="n">
         <v>-9.470000000000001</v>
@@ -1674,7 +1674,7 @@
           <t>Top sector -10%</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n">
+      <c r="B7" s="18" t="n">
         <v>-78746.98</v>
       </c>
       <c r="C7" s="20" t="n">
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>5.44</v>
+        <v>5.4</v>
       </c>
       <c r="D6" s="32" t="n">
         <v>3</v>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>0.5</v>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>34.01</v>
+        <v>34.02</v>
       </c>
       <c r="D8" s="32" t="n">
         <v>15</v>
@@ -2173,17 +2173,17 @@
           <t>MRPT</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>HAS/PFE</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>HAS</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2191,21 +2191,21 @@
       <c r="E4" s="25" t="n">
         <v>1017</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="15" t="n">
         <v>84.18000000000001</v>
       </c>
       <c r="G4" s="13" t="n">
         <v>85611.06</v>
       </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>food</t>
         </is>
       </c>
-      <c r="I4" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="I4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="17" t="inlineStr">
         <is>
           <t>low_vol_specialist</t>
         </is>
@@ -2238,7 +2238,7 @@
       <c r="F5" s="11" t="n">
         <v>26.04</v>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="G5" s="19" t="n">
         <v>-88145.39999999999</v>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -2261,17 +2261,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>KLAC/REGN</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>KLAC</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2285,15 +2285,15 @@
       <c r="G6" s="13" t="n">
         <v>129256.4</v>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="I6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="17" t="inlineStr">
         <is>
           <t>beta_neutral_long_term</t>
         </is>
@@ -2326,7 +2326,7 @@
       <c r="F7" s="4" t="n">
         <v>635.45</v>
       </c>
-      <c r="G7" s="18" t="n">
+      <c r="G7" s="19" t="n">
         <v>-14615.35</v>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -2349,17 +2349,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>KLAC/LOW</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>KLAC</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2373,15 +2373,15 @@
       <c r="G8" s="13" t="n">
         <v>81026.39999999999</v>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I8" s="16" t="n">
+      <c r="I8" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="J8" s="17" t="inlineStr">
         <is>
           <t>aggressive</t>
         </is>
@@ -2414,7 +2414,7 @@
       <c r="F9" s="4" t="n">
         <v>210.74</v>
       </c>
-      <c r="G9" s="18" t="n">
+      <c r="G9" s="19" t="n">
         <v>-80502.67999999999</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -2437,17 +2437,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>FFIV/VLTO</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>FFIV</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2461,15 +2461,15 @@
       <c r="G10" s="13" t="n">
         <v>167567.1</v>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="I10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="17" t="inlineStr">
         <is>
           <t>long_term_tilt</t>
         </is>
@@ -2502,7 +2502,7 @@
       <c r="F11" s="11" t="n">
         <v>86.05</v>
       </c>
-      <c r="G11" s="18" t="n">
+      <c r="G11" s="19" t="n">
         <v>-57223.25</v>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -2525,17 +2525,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>LRCX/BSX</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>LRCX</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2549,15 +2549,15 @@
       <c r="G12" s="13" t="n">
         <v>130713.68</v>
       </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="H12" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
+      <c r="I12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="17" t="inlineStr">
         <is>
           <t>aggressive</t>
         </is>
@@ -2590,7 +2590,7 @@
       <c r="F13" s="11" t="n">
         <v>48.55</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G13" s="19" t="n">
         <v>-82826.3</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -2613,17 +2613,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>LRCX/RMD</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>LRCX</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2637,15 +2637,15 @@
       <c r="G14" s="13" t="n">
         <v>130713.68</v>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I14" s="16" t="n">
+      <c r="I14" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J14" s="16" t="inlineStr">
+      <c r="J14" s="17" t="inlineStr">
         <is>
           <t>fast_rebalance</t>
         </is>
@@ -2678,7 +2678,7 @@
       <c r="F15" s="4" t="n">
         <v>196.04</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="G15" s="19" t="n">
         <v>-56459.52</v>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -2701,17 +2701,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>CSCO/CAG</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>CSCO</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2725,15 +2725,15 @@
       <c r="G16" s="13" t="n">
         <v>110935.68</v>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H16" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I16" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
+      <c r="I16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="17" t="inlineStr">
         <is>
           <t>fast_strict</t>
         </is>
@@ -2766,7 +2766,7 @@
       <c r="F17" s="11" t="n">
         <v>13.01</v>
       </c>
-      <c r="G17" s="18" t="n">
+      <c r="G17" s="19" t="n">
         <v>-53822.37</v>
       </c>
       <c r="H17" s="7" t="inlineStr">
@@ -2789,17 +2789,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>NUE/INTU</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>NUE</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2813,15 +2813,15 @@
       <c r="G18" s="13" t="n">
         <v>83694.31</v>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H18" s="17" t="inlineStr">
         <is>
           <t>materials</t>
         </is>
       </c>
-      <c r="I18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
+      <c r="I18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="17" t="inlineStr">
         <is>
           <t>conservative</t>
         </is>
@@ -2854,7 +2854,7 @@
       <c r="F19" s="4" t="n">
         <v>296.76</v>
       </c>
-      <c r="G19" s="18" t="n">
+      <c r="G19" s="19" t="n">
         <v>-24334.32</v>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -2877,17 +2877,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>CSCO/REGN</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>CSCO</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2901,15 +2901,15 @@
       <c r="G20" s="13" t="n">
         <v>110935.68</v>
       </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="H20" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I20" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
+      <c r="I20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="17" t="inlineStr">
         <is>
           <t>monthly_aligned_windows</t>
         </is>
@@ -2942,7 +2942,7 @@
       <c r="F21" s="4" t="n">
         <v>635.45</v>
       </c>
-      <c r="G21" s="18" t="n">
+      <c r="G21" s="19" t="n">
         <v>-56555.05</v>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -2965,17 +2965,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>NUE/MKTX</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>NUE</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2989,15 +2989,15 @@
       <c r="G22" s="13" t="n">
         <v>83694.31</v>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="H22" s="17" t="inlineStr">
         <is>
           <t>materials</t>
         </is>
       </c>
-      <c r="I22" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
+      <c r="I22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="17" t="inlineStr">
         <is>
           <t>weekly_aligned_windows</t>
         </is>
@@ -3030,7 +3030,7 @@
       <c r="F23" s="4" t="n">
         <v>116.93</v>
       </c>
-      <c r="G23" s="18" t="n">
+      <c r="G23" s="19" t="n">
         <v>-49344.46</v>
       </c>
       <c r="H23" s="7" t="inlineStr">
@@ -3053,17 +3053,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>STLD/ISRG</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>STLD</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3077,15 +3077,15 @@
       <c r="G24" s="13" t="n">
         <v>134787</v>
       </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="H24" s="17" t="inlineStr">
         <is>
           <t>materials</t>
         </is>
       </c>
-      <c r="I24" s="16" t="n">
+      <c r="I24" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J24" s="16" t="inlineStr">
+      <c r="J24" s="17" t="inlineStr">
         <is>
           <t>beta_neutral</t>
         </is>
@@ -3118,7 +3118,7 @@
       <c r="F25" s="4" t="n">
         <v>422.06</v>
       </c>
-      <c r="G25" s="18" t="n">
+      <c r="G25" s="19" t="n">
         <v>-33342.74</v>
       </c>
       <c r="H25" s="7" t="inlineStr">
@@ -3141,17 +3141,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>BWA/VLTO</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>BWA</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3159,21 +3159,21 @@
       <c r="E26" s="25" t="n">
         <v>2359</v>
       </c>
-      <c r="F26" s="17" t="n">
+      <c r="F26" s="15" t="n">
         <v>72.63</v>
       </c>
       <c r="G26" s="13" t="n">
         <v>171334.17</v>
       </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="H26" s="17" t="inlineStr">
         <is>
           <t>industrial</t>
         </is>
       </c>
-      <c r="I26" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
+      <c r="I26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="17" t="inlineStr">
         <is>
           <t>kalman_aggressive</t>
         </is>
@@ -3206,7 +3206,7 @@
       <c r="F27" s="11" t="n">
         <v>86.05</v>
       </c>
-      <c r="G27" s="18" t="n">
+      <c r="G27" s="19" t="n">
         <v>-82694.05</v>
       </c>
       <c r="H27" s="7" t="inlineStr">
@@ -3229,17 +3229,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>STLD/HII</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>STLD</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3253,15 +3253,15 @@
       <c r="G28" s="13" t="n">
         <v>134787</v>
       </c>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="H28" s="17" t="inlineStr">
         <is>
           <t>materials</t>
         </is>
       </c>
-      <c r="I28" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="16" t="inlineStr">
+      <c r="I28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="17" t="inlineStr">
         <is>
           <t>weekly_aligned_windows</t>
         </is>
@@ -3294,7 +3294,7 @@
       <c r="F29" s="4" t="n">
         <v>293.04</v>
       </c>
-      <c r="G29" s="18" t="n">
+      <c r="G29" s="19" t="n">
         <v>-52161.12</v>
       </c>
       <c r="H29" s="7" t="inlineStr">
@@ -3317,17 +3317,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>BWA/CME</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C30" s="17" t="inlineStr">
         <is>
           <t>BWA</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3335,21 +3335,21 @@
       <c r="E30" s="25" t="n">
         <v>2359</v>
       </c>
-      <c r="F30" s="17" t="n">
+      <c r="F30" s="15" t="n">
         <v>72.63</v>
       </c>
       <c r="G30" s="13" t="n">
         <v>171334.17</v>
       </c>
-      <c r="H30" s="16" t="inlineStr">
+      <c r="H30" s="17" t="inlineStr">
         <is>
           <t>industrial</t>
         </is>
       </c>
-      <c r="I30" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
+      <c r="I30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="17" t="inlineStr">
         <is>
           <t>kalman_aggressive</t>
         </is>
@@ -3382,7 +3382,7 @@
       <c r="F31" s="4" t="n">
         <v>257.4</v>
       </c>
-      <c r="G31" s="18" t="n">
+      <c r="G31" s="19" t="n">
         <v>-76705.2</v>
       </c>
       <c r="H31" s="7" t="inlineStr">
@@ -3475,26 +3475,26 @@
           <t>MRPT</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>HAS/PFE</t>
         </is>
       </c>
-      <c r="C4" s="19" t="n">
+      <c r="C4" s="18" t="n">
         <v>-1479.68</v>
       </c>
       <c r="D4" s="13" t="n">
         <v>173756.46</v>
       </c>
-      <c r="E4" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="E4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>low_vol_specialist</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3511,7 +3511,7 @@
           <t>KLAC/REGN</t>
         </is>
       </c>
-      <c r="C5" s="18" t="n">
+      <c r="C5" s="19" t="n">
         <v>-5525.82</v>
       </c>
       <c r="D5" s="4" t="n">
@@ -3537,7 +3537,7 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>KLAC/LOW</t>
         </is>
@@ -3548,15 +3548,15 @@
       <c r="D6" s="13" t="n">
         <v>161529.08</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>aggressive</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3599,26 +3599,26 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>LRCX/BSX</t>
         </is>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="18" t="n">
         <v>-6831.34</v>
       </c>
       <c r="D8" s="13" t="n">
         <v>213539.98</v>
       </c>
-      <c r="E8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="E8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>aggressive</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3635,7 +3635,7 @@
           <t>LRCX/RMD</t>
         </is>
       </c>
-      <c r="C9" s="18" t="n">
+      <c r="C9" s="19" t="n">
         <v>-7997.26</v>
       </c>
       <c r="D9" s="4" t="n">
@@ -3661,7 +3661,7 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>CSCO/CAG</t>
         </is>
@@ -3672,15 +3672,15 @@
       <c r="D10" s="13" t="n">
         <v>164758.05</v>
       </c>
-      <c r="E10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="E10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>fast_strict</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3723,26 +3723,26 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>CSCO/REGN</t>
         </is>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="C12" s="18" t="n">
         <v>-726.99</v>
       </c>
       <c r="D12" s="13" t="n">
         <v>167490.73</v>
       </c>
-      <c r="E12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="E12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>monthly_aligned_windows</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3785,7 +3785,7 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>STLD/ISRG</t>
         </is>
@@ -3796,15 +3796,15 @@
       <c r="D14" s="13" t="n">
         <v>168129.74</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>beta_neutral</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G14" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3821,7 +3821,7 @@
           <t>BWA/VLTO</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="19" t="n">
         <v>-1359.2</v>
       </c>
       <c r="D15" s="4" t="n">
@@ -3847,7 +3847,7 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>STLD/HII</t>
         </is>
@@ -3858,15 +3858,15 @@
       <c r="D16" s="13" t="n">
         <v>186948.12</v>
       </c>
-      <c r="E16" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="E16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>weekly_aligned_windows</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G16" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3972,12 +3972,12 @@
           <t>T_1D</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
@@ -4006,12 +4006,12 @@
           <t>T_1M</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
@@ -4096,16 +4096,16 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>15.51</v>
+        <v>15.43</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>25</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>-15.27</v>
+        <v>-15.19</v>
       </c>
     </row>
     <row r="7">
@@ -4114,17 +4114,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>11.74</v>
-      </c>
-      <c r="C7" s="16" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="D7" s="16" t="n">
+      <c r="B7" s="17" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="D7" s="17" t="n">
         <v>25</v>
       </c>
       <c r="E7" s="21" t="n">
-        <v>4.16</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="8">
@@ -4137,13 +4137,13 @@
         <v>26.02</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>4.07</v>
+        <v>4.06</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>-21.95</v>
+        <v>-21.96</v>
       </c>
     </row>
     <row r="9">
@@ -4152,17 +4152,17 @@
           <t>AISS</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>46.73</v>
       </c>
-      <c r="C9" s="16" t="n">
-        <v>79.79000000000001</v>
-      </c>
-      <c r="D9" s="16" t="n">
+      <c r="C9" s="17" t="n">
+        <v>79.67</v>
+      </c>
+      <c r="D9" s="17" t="n">
         <v>25</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>33.06</v>
+        <v>32.93</v>
       </c>
     </row>
     <row r="11">
@@ -4200,7 +4200,7 @@
           <t>LRCX/RMD</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>13.34</v>
       </c>
     </row>
@@ -4220,7 +4220,7 @@
           <t>KLAC/LOW</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>7.4</v>
       </c>
     </row>
@@ -4240,7 +4240,7 @@
           <t>STLD/ISRG</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>6.77</v>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
           <t>BWA/CME</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>6.35</v>
       </c>
     </row>
@@ -4280,7 +4280,7 @@
           <t>CSCO/REGN</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
+      <c r="B22" s="17" t="n">
         <v>5.31</v>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
           <t>NUE/MKTX</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
+      <c r="B24" s="17" t="n">
         <v>4.24</v>
       </c>
     </row>
@@ -4320,7 +4320,7 @@
           <t>HAS/PFE</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
+      <c r="B26" s="17" t="n">
         <v>0.32</v>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="B5" s="27" t="n">
-        <v>39.03</v>
+        <v>38.97</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>2.6</v>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>0.072 (t=0.59)</t>
+          <t>0.073 (t=0.6)</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>-0.112 (t=-0.63)</t>
+          <t>-0.111 (t=-0.62)</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -4481,45 +4481,45 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>49.05</v>
-      </c>
-      <c r="C6" s="16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="D6" s="16" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="E6" s="16" t="n">
+        <v>48.07</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="E6" s="17" t="n">
         <v>116</v>
       </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>0.048 (t=0.34)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>-0.105 (t=-0.48)</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>-0.063 (t=-0.33)</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>0.234 (t=1.29)</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>-0.203 (t=-0.71)</t>
-        </is>
-      </c>
-      <c r="K6" s="16" t="inlineStr">
-        <is>
-          <t>-0.139 (t=-1.36)</t>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>0.056 (t=0.39)</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>-0.116 (t=-0.52)</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>-0.06 (t=-0.31)</t>
+        </is>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>0.241 (t=1.31)</t>
+        </is>
+      </c>
+      <c r="J6" s="17" t="inlineStr">
+        <is>
+          <t>-0.207 (t=-0.72)</t>
+        </is>
+      </c>
+      <c r="K6" s="17" t="inlineStr">
+        <is>
+          <t>-0.141 (t=-1.36)</t>
         </is>
       </c>
     </row>
@@ -4530,45 +4530,45 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>27.25</v>
+        <v>28.62</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0.038</v>
+        <v>0.036</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>116</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>-0.057 (t=-0.37)</t>
+          <t>-0.069 (t=-0.42)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>-0.018 (t=-0.07)</t>
+          <t>-0.004 (t=-0.02)</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>0.239 (t=1.1)</t>
+          <t>0.235 (t=1.04)</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>-0.092 (t=-0.45)</t>
+          <t>-0.103 (t=-0.49)</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>0.017 (t=0.05)</t>
+          <t>0.022 (t=0.07)</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>-0.068 (t=-0.59)</t>
+          <t>-0.065 (t=-0.55)</t>
         </is>
       </c>
     </row>
@@ -4657,10 +4657,10 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>-0.196</v>
+        <v>-0.186</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>29.453</v>
+        <v>29.655</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>0</v>
@@ -4669,10 +4669,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>2.15</v>
+        <v>2.161</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>2.15</v>
+        <v>2.161</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>0</v>
@@ -4684,26 +4684,26 @@
           <t>MRPT</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>-0.296</v>
-      </c>
-      <c r="C5" s="16" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="D5" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="16" t="b">
+      <c r="B5" s="17" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>2.284</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="F5" s="16" t="n">
-        <v>1.578</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H5" s="16" t="n">
-        <v>0.042</v>
+      <c r="F5" s="17" t="n">
+        <v>1.601</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>1.664</v>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>0.063</v>
       </c>
     </row>
     <row r="6">
@@ -4713,10 +4713,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1.398</v>
+        <v>1.409</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>37.225</v>
+        <v>36.625</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>0</v>
@@ -4725,10 +4725,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>4.583</v>
+        <v>4.599</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>4.583</v>
+        <v>4.599</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>0</v>
@@ -4793,31 +4793,31 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>0.7302999999999999</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>1058</v>
+        <v>1068</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>8.84</v>
+        <v>8.85</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>9.460000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>75.8</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>2.516</v>
+        <v>2.517</v>
       </c>
     </row>
     <row r="10">
@@ -4826,32 +4826,32 @@
           <t>MRPT</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
-        <v>1.338</v>
-      </c>
-      <c r="C10" s="16" t="n">
-        <v>0.8427</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>394</v>
-      </c>
-      <c r="E10" s="16" t="n">
+      <c r="B10" s="17" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>442</v>
+      </c>
+      <c r="E10" s="17" t="n">
         <v>8.76</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="17" t="n">
         <v>9.550000000000001</v>
       </c>
-      <c r="G10" s="16" t="n">
+      <c r="G10" s="17" t="n">
         <v>76.5</v>
       </c>
-      <c r="H10" s="16" t="n">
-        <v>6.39</v>
-      </c>
-      <c r="I10" s="16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J10" s="16" t="n">
-        <v>0.303</v>
+      <c r="H10" s="17" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>0.305</v>
       </c>
     </row>
     <row r="11">
@@ -4861,13 +4861,13 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>0.416</v>
+        <v>0.442</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>0.6264999999999999</v>
+        <v>0.6341</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>3822</v>
+        <v>3388</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>15.56</v>
@@ -4876,16 +4876,16 @@
         <v>18.48</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>79.90000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>5.441</v>
+        <v>5.404</v>
       </c>
     </row>
   </sheetData>
@@ -4969,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>386751.68</v>
+        <v>370553.66</v>
       </c>
     </row>
     <row r="6">
@@ -5026,7 +5026,7 @@
         <v>2502811.9</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>1844161.87</v>
+        <v>1827963.86</v>
       </c>
     </row>
     <row r="9">
@@ -5051,452 +5051,452 @@
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Short Collateral Due 担保差额 2%</t>
+          <t>Margin Loan 保证金借款</t>
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>16174.64</v>
+        <v>735309.64</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>16378.21</v>
+        <v>769208.33</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>18990.13</v>
-      </c>
-      <c r="E10" s="13" t="n">
-        <v>15765.27</v>
+        <v>563958.29</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Margin Loan 保证金借款</t>
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Total Liabilities 总负债</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>718973.39</v>
+        <v>1544041.45</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>753303.92</v>
+        <v>1588118.79</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>544625.96</v>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>0</v>
+        <v>1513464.55</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>788263.47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>Total Liabilities 总负债</t>
+          <t>NAV (Equity) 净值 = TA - TL</t>
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1543879.84</v>
+        <v>1007255.64</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>1588592.59</v>
+        <v>1111711.73</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1513122.34</v>
+        <v>989347.35</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>804028.73</v>
+        <v>1039700.39</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>NAV (Equity) 净值 = TA - TL</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>1007417.25</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>1111237.93</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>989689.5600000001</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>1040133.14</v>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Gross Leverage 总杠杆 (x)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>2.414</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>2.511</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>1.387</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Gross Leverage 总杠杆 (x)</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>2.516</v>
-      </c>
-      <c r="C14" s="16" t="n">
-        <v>2.415</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>1.386</v>
+          <t>Net Leverage 净杠杆 (x)</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>Net Leverage 净杠杆 (x)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n">
-        <v>0.911</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>0.9409999999999999</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>0.591</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>-0.13</v>
+          <t>PM Requirement (20%)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>507024.49</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>536690.46</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>496764.36</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>288328.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>PM Requirement (20%)</t>
+          <t>Excess Liquidity 超额流动性</t>
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>507024.49</v>
+        <v>500231.15</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>536690.46</v>
+        <v>575021.27</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>496764.36</v>
+        <v>492582.99</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>288328.99</v>
+        <v>751371.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Excess Liquidity 超额流动性</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>500392.76</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>574547.47</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>492925.2</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>751804.15</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
           <t>Balance Check (≈0)</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>0</v>
+      <c r="B17" s="7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>COMBINED — 双账户法</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>COMBINED — 双账户法</t>
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>T (今日)</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>T-1D (前日)</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>T-1W (上周)</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>T-1M (上月)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>T (今日)</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>T-1D (前日)</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>T-1W (上周)</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>T-1M (上月)</t>
-        </is>
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Long Book — Allocated Capital 分配资本</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>1007255.64</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>1111711.73</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>989347.35</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>653381.46</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>Long Book — Allocated Capital 分配资本</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>686040.12</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>772120.9</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>611354.67</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>471408.53</v>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Long Book — Cash 现金</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>Long Book — Cash 现金</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>0</v>
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Long Book — Market Value 市值</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>1726390.64</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>1864541.85</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>1534315.52</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>653381.46</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>Long Book — Market Value 市值</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>1726390.64</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>1864541.85</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>1534315.52</v>
-      </c>
-      <c r="E24" s="4" t="n">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Long Book — Margin Loan 融资</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="n">
+        <v>719135</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>752830.12</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>544968.17</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Long Book — NAV</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>1007255.64</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>1111711.73</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>989347.35</v>
+      </c>
+      <c r="E25" s="4" t="n">
         <v>653381.46</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>Long Book — Margin Loan 融资</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="n">
-        <v>1040350.52</v>
-      </c>
-      <c r="C25" s="13" t="n">
-        <v>1092420.95</v>
-      </c>
-      <c r="D25" s="13" t="n">
-        <v>922960.84</v>
-      </c>
-      <c r="E25" s="13" t="n">
-        <v>181972.94</v>
-      </c>
-    </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Long Book — NAV</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>686040.12</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>772120.9</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>611354.67</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>471408.53</v>
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Allocated Capital 分配资本</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>15765.27</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>Short Book — Allocated Capital 分配资本</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="n">
-        <v>321377.13</v>
-      </c>
-      <c r="C27" s="13" t="n">
-        <v>339117.03</v>
-      </c>
-      <c r="D27" s="13" t="n">
-        <v>378334.89</v>
-      </c>
-      <c r="E27" s="13" t="n">
-        <v>568724.61</v>
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Short Book — Collateral 担保金</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>15765.27</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Short Book — Collateral 担保金</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>321377.13</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>339117.03</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>378334.89</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>568724.61</v>
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Short Proceeds 做空收入</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="n">
+        <v>808731.8100000001</v>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>818910.46</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>949506.26</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>788263.47</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>Short Book — Short Proceeds 做空收入</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="n">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Short Book — Market Value 市值(负债)</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
         <v>808731.8100000001</v>
       </c>
-      <c r="C29" s="13" t="n">
+      <c r="C29" s="4" t="n">
         <v>818910.46</v>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="4" t="n">
         <v>949506.26</v>
       </c>
-      <c r="E29" s="13" t="n">
+      <c r="E29" s="4" t="n">
         <v>788263.47</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>Short Book — Market Value 市值(负债)</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>808731.8100000001</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>818910.46</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>949506.26</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>788263.47</v>
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Margin Loan 融资(2%)</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="n">
+        <v>16174.64</v>
+      </c>
+      <c r="C30" s="13" t="n">
+        <v>16378.21</v>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>18990.13</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Short Book — NAV</t>
         </is>
       </c>
-      <c r="B31" s="13" t="n">
-        <v>321377.13</v>
-      </c>
-      <c r="C31" s="13" t="n">
-        <v>339117.03</v>
-      </c>
-      <c r="D31" s="13" t="n">
-        <v>378334.89</v>
-      </c>
-      <c r="E31" s="13" t="n">
-        <v>568724.61</v>
+      <c r="B31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>15765.27</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>Unallocated Cash 未分配现金</t>
         </is>
       </c>
-      <c r="B32" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="11" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E32" s="11" t="n">
-        <v>0</v>
+      <c r="B32" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>370553.66</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Dual-View NAV 双账户法NAV</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n">
-        <v>1007417.25</v>
-      </c>
-      <c r="C33" s="13" t="n">
-        <v>1111237.93</v>
-      </c>
-      <c r="D33" s="13" t="n">
-        <v>989689.5600000001</v>
-      </c>
-      <c r="E33" s="13" t="n">
-        <v>1040133.14</v>
+      <c r="B33" s="4" t="n">
+        <v>1007255.64</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>1111711.73</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>989347.35</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>1039700.39</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>NAV Alignment Check (≈0)</t>
         </is>
       </c>
-      <c r="B34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="7" t="n">
+      <c r="B34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5541,16 +5541,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>487811.06</v>
+        <v>482954.15</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>482975.45</v>
+        <v>478172.49</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>426399.58</v>
+        <v>420313.98</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>525461.14</v>
+        <v>520326.12</v>
       </c>
     </row>
     <row r="40">
@@ -5598,16 +5598,16 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>663330.4300000001</v>
+        <v>658473.52</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>664520.35</v>
+        <v>659717.39</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>729621.71</v>
+        <v>723536.11</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>706870.29</v>
+        <v>701735.27</v>
       </c>
     </row>
     <row r="43">
@@ -5632,452 +5632,452 @@
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>Short Collateral Due 担保差额 2%</t>
-        </is>
-      </c>
-      <c r="B44" s="13" t="n">
-        <v>1762.91</v>
-      </c>
-      <c r="C44" s="13" t="n">
-        <v>1679.62</v>
-      </c>
-      <c r="D44" s="13" t="n">
-        <v>2964.59</v>
-      </c>
-      <c r="E44" s="13" t="n">
-        <v>1822.48</v>
+          <t>Margin Loan 保证金借款</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>Margin Loan 保证金借款</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="11" t="n">
-        <v>0</v>
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>Total Liabilities 总负债</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>88145.39999999999</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>83981.03999999999</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>148229.6</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>91124</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>Total Liabilities 总负债</t>
+          <t>NAV (Equity) 净值 = TA - TL</t>
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>89908.31</v>
+        <v>570328.12</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>85660.66</v>
+        <v>575736.35</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>151194.19</v>
+        <v>575306.51</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>92946.48</v>
+        <v>610611.27</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>NAV (Equity) 净值 = TA - TL</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="n">
-        <v>573422.12</v>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>578859.6899999999</v>
-      </c>
-      <c r="D47" s="4" t="n">
-        <v>578427.52</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>613923.8100000001</v>
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>Gross Leverage 总杠杆 (x)</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>0.294</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>Gross Leverage 总杠杆 (x)</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="n">
-        <v>0.303</v>
-      </c>
-      <c r="C48" s="16" t="n">
-        <v>0.311</v>
-      </c>
-      <c r="D48" s="16" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="E48" s="16" t="n">
-        <v>0.293</v>
+          <t>Net Leverage 净杠杆 (x)</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="D48" s="17" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>-0.004</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>Net Leverage 净杠杆 (x)</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="C49" s="7" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="D49" s="7" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="E49" s="7" t="n">
-        <v>-0.004</v>
+          <t>PM Requirement (20%)</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>34751.29</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>35973.06</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>60051.51</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>35917.33</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>PM Requirement (20%)</t>
+          <t>Excess Liquidity 超额流动性</t>
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>34751.29</v>
+        <v>535576.83</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>35973.06</v>
+        <v>539763.29</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>60051.51</v>
+        <v>515255</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>35917.33</v>
+        <v>574693.9399999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>Excess Liquidity 超额流动性</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n">
-        <v>538670.83</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>542886.63</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>518376.01</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>578006.48</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="12" t="inlineStr">
-        <is>
           <t>Balance Check (≈0)</t>
         </is>
       </c>
-      <c r="B52" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C52" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="16" t="n">
-        <v>0</v>
+      <c r="B51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>MRPT — 双账户法</t>
+        </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>MRPT — 双账户法</t>
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>T (今日)</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>T-1D (前日)</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>T-1W (上周)</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>T-1M (上月)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>T (今日)</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>T-1D (前日)</t>
-        </is>
-      </c>
-      <c r="D55" s="9" t="inlineStr">
-        <is>
-          <t>T-1W (上周)</t>
-        </is>
-      </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t>T-1M (上月)</t>
-        </is>
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>Long Book — Allocated Capital 分配资本</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>85611.06</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>95884.24000000001</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>152027.94</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>88462.67</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="inlineStr">
-        <is>
-          <t>Long Book — Allocated Capital 分配资本</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="n">
-        <v>282529.21</v>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>308583.85</v>
-      </c>
-      <c r="D56" s="4" t="n">
-        <v>292872.39</v>
-      </c>
-      <c r="E56" s="4" t="n">
-        <v>302412.98</v>
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>Long Book — Cash 现金</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="12" t="inlineStr">
-        <is>
-          <t>Long Book — Cash 现金</t>
-        </is>
-      </c>
-      <c r="B57" s="13" t="n">
-        <v>196918.15</v>
-      </c>
-      <c r="C57" s="13" t="n">
-        <v>212699.61</v>
-      </c>
-      <c r="D57" s="13" t="n">
-        <v>140844.45</v>
-      </c>
-      <c r="E57" s="13" t="n">
-        <v>213950.31</v>
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>Long Book — Market Value 市值</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n">
+        <v>85611.06</v>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>95884.24000000001</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>152027.94</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>88462.67</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>Long Book — Market Value 市值</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="n">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>Long Book — Margin Loan 融资</t>
+        </is>
+      </c>
+      <c r="B58" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="16" t="inlineStr">
+        <is>
+          <t>Long Book — NAV</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n">
         <v>85611.06</v>
       </c>
-      <c r="C58" s="4" t="n">
+      <c r="C59" s="4" t="n">
         <v>95884.24000000001</v>
       </c>
-      <c r="D58" s="4" t="n">
+      <c r="D59" s="4" t="n">
         <v>152027.94</v>
       </c>
-      <c r="E58" s="4" t="n">
+      <c r="E59" s="4" t="n">
         <v>88462.67</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>Long Book — Margin Loan 融资</t>
-        </is>
-      </c>
-      <c r="B59" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C59" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="60">
-      <c r="A60" s="15" t="inlineStr">
-        <is>
-          <t>Long Book — NAV</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="n">
-        <v>282529.21</v>
-      </c>
-      <c r="C60" s="4" t="n">
-        <v>308583.85</v>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>292872.39</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>302412.98</v>
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Allocated Capital 分配资本</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="n">
+        <v>1762.91</v>
+      </c>
+      <c r="C60" s="13" t="n">
+        <v>1679.62</v>
+      </c>
+      <c r="D60" s="13" t="n">
+        <v>2964.59</v>
+      </c>
+      <c r="E60" s="13" t="n">
+        <v>1822.48</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="12" t="inlineStr">
-        <is>
-          <t>Short Book — Allocated Capital 分配资本</t>
-        </is>
-      </c>
-      <c r="B61" s="13" t="n">
-        <v>290892.91</v>
-      </c>
-      <c r="C61" s="13" t="n">
-        <v>270275.84</v>
-      </c>
-      <c r="D61" s="13" t="n">
-        <v>285555.13</v>
-      </c>
-      <c r="E61" s="13" t="n">
-        <v>311510.83</v>
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>Short Book — Collateral 担保金</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="n">
+        <v>1762.91</v>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>1679.62</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>2964.59</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>1822.48</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>Short Book — Collateral 担保金</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="n">
-        <v>290892.91</v>
-      </c>
-      <c r="C62" s="4" t="n">
-        <v>270275.84</v>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>285555.13</v>
-      </c>
-      <c r="E62" s="4" t="n">
-        <v>311510.83</v>
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Short Proceeds 做空收入</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="n">
+        <v>88145.39999999999</v>
+      </c>
+      <c r="C62" s="13" t="n">
+        <v>83981.03999999999</v>
+      </c>
+      <c r="D62" s="13" t="n">
+        <v>148229.6</v>
+      </c>
+      <c r="E62" s="13" t="n">
+        <v>91124</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>Short Book — Short Proceeds 做空收入</t>
-        </is>
-      </c>
-      <c r="B63" s="13" t="n">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>Short Book — Market Value 市值(负债)</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="n">
         <v>88145.39999999999</v>
       </c>
-      <c r="C63" s="13" t="n">
+      <c r="C63" s="4" t="n">
         <v>83981.03999999999</v>
       </c>
-      <c r="D63" s="13" t="n">
+      <c r="D63" s="4" t="n">
         <v>148229.6</v>
       </c>
-      <c r="E63" s="13" t="n">
+      <c r="E63" s="4" t="n">
         <v>91124</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>Short Book — Market Value 市值(负债)</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="n">
-        <v>88145.39999999999</v>
-      </c>
-      <c r="C64" s="4" t="n">
-        <v>83981.03999999999</v>
-      </c>
-      <c r="D64" s="4" t="n">
-        <v>148229.6</v>
-      </c>
-      <c r="E64" s="4" t="n">
-        <v>91124</v>
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Margin Loan 融资(2%)</t>
+        </is>
+      </c>
+      <c r="B64" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="14" t="inlineStr">
+      <c r="A65" s="16" t="inlineStr">
         <is>
           <t>Short Book — NAV</t>
         </is>
       </c>
-      <c r="B65" s="13" t="n">
-        <v>290892.91</v>
-      </c>
-      <c r="C65" s="13" t="n">
-        <v>270275.84</v>
-      </c>
-      <c r="D65" s="13" t="n">
-        <v>285555.13</v>
-      </c>
-      <c r="E65" s="13" t="n">
-        <v>311510.83</v>
+      <c r="B65" s="4" t="n">
+        <v>1762.91</v>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>1679.62</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>2964.59</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>1822.48</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="10" t="inlineStr">
+      <c r="A66" s="12" t="inlineStr">
         <is>
           <t>Unallocated Cash 未分配现金</t>
         </is>
       </c>
-      <c r="B66" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C66" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="11" t="n">
-        <v>-0</v>
+      <c r="B66" s="13" t="n">
+        <v>482954.15</v>
+      </c>
+      <c r="C66" s="13" t="n">
+        <v>478172.49</v>
+      </c>
+      <c r="D66" s="13" t="n">
+        <v>420313.98</v>
+      </c>
+      <c r="E66" s="13" t="n">
+        <v>520326.12</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="14" t="inlineStr">
+      <c r="A67" s="16" t="inlineStr">
         <is>
           <t>Dual-View NAV 双账户法NAV</t>
         </is>
       </c>
-      <c r="B67" s="13" t="n">
-        <v>573422.12</v>
-      </c>
-      <c r="C67" s="13" t="n">
-        <v>578859.6899999999</v>
-      </c>
-      <c r="D67" s="13" t="n">
-        <v>578427.52</v>
-      </c>
-      <c r="E67" s="13" t="n">
-        <v>613923.8100000001</v>
+      <c r="B67" s="4" t="n">
+        <v>570328.12</v>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>575736.35</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>575306.51</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>610611.27</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="10" t="inlineStr">
+      <c r="A68" s="12" t="inlineStr">
         <is>
           <t>NAV Alignment Check (≈0)</t>
         </is>
       </c>
-      <c r="B68" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C68" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="7" t="n">
+      <c r="B68" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6213,452 +6213,452 @@
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
         <is>
-          <t>Short Collateral Due 担保差额 2%</t>
+          <t>Margin Loan 保证金借款</t>
         </is>
       </c>
       <c r="B78" s="13" t="n">
-        <v>14411.73</v>
+        <v>1218263.78</v>
       </c>
       <c r="C78" s="13" t="n">
-        <v>14698.59</v>
+        <v>1247380.81</v>
       </c>
       <c r="D78" s="13" t="n">
-        <v>16025.53</v>
+        <v>984272.27</v>
       </c>
       <c r="E78" s="13" t="n">
-        <v>13942.79</v>
+        <v>149772.46</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>Margin Loan 保证金借款</t>
+      <c r="A79" s="16" t="inlineStr">
+        <is>
+          <t>Total Liabilities 总负债</t>
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>1206784.45</v>
+        <v>1938850.19</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>1236279.37</v>
+        <v>1982310.23</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>971025.54</v>
+        <v>1785548.93</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>138709.46</v>
+        <v>846911.9300000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>Total Liabilities 总负债</t>
+          <t>NAV (Equity) 净值 = TA - TL</t>
         </is>
       </c>
       <c r="B80" s="13" t="n">
-        <v>1941782.59</v>
+        <v>436927.53</v>
       </c>
       <c r="C80" s="13" t="n">
-        <v>1985907.38</v>
+        <v>535975.39</v>
       </c>
       <c r="D80" s="13" t="n">
-        <v>1788327.73</v>
+        <v>414040.84</v>
       </c>
       <c r="E80" s="13" t="n">
-        <v>849791.72</v>
+        <v>429089.12</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="15" t="inlineStr">
-        <is>
-          <t>NAV (Equity) 净值 = TA - TL</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="n">
-        <v>433995.13</v>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>532378.24</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>411262.04</v>
-      </c>
-      <c r="E81" s="4" t="n">
-        <v>426209.33</v>
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>Gross Leverage 总杠杆 (x)</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="n">
+        <v>5.404</v>
+      </c>
+      <c r="C81" s="7" t="n">
+        <v>4.671</v>
+      </c>
+      <c r="D81" s="7" t="n">
+        <v>5.274</v>
+      </c>
+      <c r="E81" s="7" t="n">
+        <v>2.941</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
         <is>
-          <t>Gross Leverage 总杠杆 (x)</t>
-        </is>
-      </c>
-      <c r="B82" s="16" t="n">
-        <v>5.441</v>
-      </c>
-      <c r="C82" s="16" t="n">
-        <v>4.703</v>
-      </c>
-      <c r="D82" s="16" t="n">
-        <v>5.309</v>
-      </c>
-      <c r="E82" s="16" t="n">
-        <v>2.961</v>
+          <t>Net Leverage 净杠杆 (x)</t>
+        </is>
+      </c>
+      <c r="B82" s="17" t="n">
+        <v>2.106</v>
+      </c>
+      <c r="C82" s="17" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="D82" s="17" t="n">
+        <v>1.403</v>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>-0.308</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>Net Leverage 净杠杆 (x)</t>
-        </is>
-      </c>
-      <c r="B83" s="7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="C83" s="7" t="n">
-        <v>1.942</v>
-      </c>
-      <c r="D83" s="7" t="n">
-        <v>1.413</v>
-      </c>
-      <c r="E83" s="7" t="n">
-        <v>-0.31</v>
+          <t>PM Requirement (20%)</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="n">
+        <v>472273.2</v>
+      </c>
+      <c r="C83" s="4" t="n">
+        <v>500717.41</v>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>436712.85</v>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>252411.65</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
         <is>
-          <t>PM Requirement (20%)</t>
-        </is>
-      </c>
-      <c r="B84" s="13" t="n">
-        <v>472273.2</v>
+          <t>Excess Liquidity 超额流动性</t>
+        </is>
+      </c>
+      <c r="B84" s="18" t="n">
+        <v>-35345.67</v>
       </c>
       <c r="C84" s="13" t="n">
-        <v>500717.41</v>
-      </c>
-      <c r="D84" s="13" t="n">
-        <v>436712.85</v>
+        <v>35257.98</v>
+      </c>
+      <c r="D84" s="18" t="n">
+        <v>-22672.01</v>
       </c>
       <c r="E84" s="13" t="n">
-        <v>252411.65</v>
+        <v>176677.47</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>Excess Liquidity 超额流动性</t>
-        </is>
-      </c>
-      <c r="B85" s="18" t="n">
-        <v>-38278.07</v>
-      </c>
-      <c r="C85" s="4" t="n">
-        <v>31660.83</v>
-      </c>
-      <c r="D85" s="18" t="n">
-        <v>-25450.81</v>
-      </c>
-      <c r="E85" s="4" t="n">
-        <v>173797.68</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="12" t="inlineStr">
-        <is>
           <t>Balance Check (≈0)</t>
         </is>
       </c>
-      <c r="B86" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C86" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="16" t="n">
-        <v>0</v>
+      <c r="B85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>MTFS — 双账户法</t>
+        </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="8" t="inlineStr">
-        <is>
-          <t>MTFS — 双账户法</t>
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>T (今日)</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>T-1D (前日)</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>T-1W (上周)</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t>T-1M (上月)</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="9" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B89" s="9" t="inlineStr">
-        <is>
-          <t>T (今日)</t>
-        </is>
-      </c>
-      <c r="C89" s="9" t="inlineStr">
-        <is>
-          <t>T-1D (前日)</t>
-        </is>
-      </c>
-      <c r="D89" s="9" t="inlineStr">
-        <is>
-          <t>T-1W (上周)</t>
-        </is>
-      </c>
-      <c r="E89" s="9" t="inlineStr">
-        <is>
-          <t>T-1M (上月)</t>
-        </is>
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>Long Book — Allocated Capital 分配资本</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="n">
+        <v>436927.53</v>
+      </c>
+      <c r="C89" s="4" t="n">
+        <v>535975.39</v>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>414040.84</v>
+      </c>
+      <c r="E89" s="4" t="n">
+        <v>429089.12</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="10" t="inlineStr">
-        <is>
-          <t>Long Book — Allocated Capital 分配资本</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="n">
-        <v>301558.65</v>
-      </c>
-      <c r="C90" s="4" t="n">
-        <v>376098.3</v>
-      </c>
-      <c r="D90" s="4" t="n">
-        <v>260346.09</v>
-      </c>
-      <c r="E90" s="4" t="n">
-        <v>190778.56</v>
+      <c r="A90" s="12" t="inlineStr">
+        <is>
+          <t>Long Book — Cash 现金</t>
+        </is>
+      </c>
+      <c r="B90" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="12" t="inlineStr">
-        <is>
-          <t>Long Book — Cash 现金</t>
-        </is>
-      </c>
-      <c r="B91" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C91" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" s="17" t="n">
-        <v>0</v>
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>Long Book — Market Value 市值</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="n">
+        <v>1640779.58</v>
+      </c>
+      <c r="C91" s="4" t="n">
+        <v>1768657.61</v>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>1382287.58</v>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>564918.79</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="10" t="inlineStr">
-        <is>
-          <t>Long Book — Market Value 市值</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="n">
-        <v>1640779.58</v>
-      </c>
-      <c r="C92" s="4" t="n">
-        <v>1768657.61</v>
-      </c>
-      <c r="D92" s="4" t="n">
-        <v>1382287.58</v>
-      </c>
-      <c r="E92" s="4" t="n">
-        <v>564918.79</v>
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t>Long Book — Margin Loan 融资</t>
+        </is>
+      </c>
+      <c r="B92" s="13" t="n">
+        <v>1203852.05</v>
+      </c>
+      <c r="C92" s="13" t="n">
+        <v>1232682.22</v>
+      </c>
+      <c r="D92" s="13" t="n">
+        <v>968246.74</v>
+      </c>
+      <c r="E92" s="13" t="n">
+        <v>135829.67</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="12" t="inlineStr">
-        <is>
-          <t>Long Book — Margin Loan 融资</t>
-        </is>
-      </c>
-      <c r="B93" s="13" t="n">
-        <v>1339220.93</v>
-      </c>
-      <c r="C93" s="13" t="n">
-        <v>1392559.31</v>
-      </c>
-      <c r="D93" s="13" t="n">
-        <v>1121941.49</v>
-      </c>
-      <c r="E93" s="13" t="n">
-        <v>374140.23</v>
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>Long Book — NAV</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="n">
+        <v>436927.53</v>
+      </c>
+      <c r="C93" s="4" t="n">
+        <v>535975.39</v>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>414040.84</v>
+      </c>
+      <c r="E93" s="4" t="n">
+        <v>429089.12</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="15" t="inlineStr">
-        <is>
-          <t>Long Book — NAV</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="n">
-        <v>301558.65</v>
-      </c>
-      <c r="C94" s="4" t="n">
-        <v>376098.3</v>
-      </c>
-      <c r="D94" s="4" t="n">
-        <v>260346.09</v>
-      </c>
-      <c r="E94" s="4" t="n">
-        <v>190778.56</v>
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Allocated Capital 分配资本</t>
+        </is>
+      </c>
+      <c r="B94" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="12" t="inlineStr">
-        <is>
-          <t>Short Book — Allocated Capital 分配资本</t>
-        </is>
-      </c>
-      <c r="B95" s="13" t="n">
-        <v>132436.48</v>
-      </c>
-      <c r="C95" s="13" t="n">
-        <v>156279.94</v>
-      </c>
-      <c r="D95" s="13" t="n">
-        <v>150915.95</v>
-      </c>
-      <c r="E95" s="13" t="n">
-        <v>235430.77</v>
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>Short Book — Collateral 担保金</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="10" t="inlineStr">
-        <is>
-          <t>Short Book — Collateral 担保金</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="n">
-        <v>132436.48</v>
-      </c>
-      <c r="C96" s="4" t="n">
-        <v>156279.94</v>
-      </c>
-      <c r="D96" s="4" t="n">
-        <v>150915.95</v>
-      </c>
-      <c r="E96" s="4" t="n">
-        <v>235430.77</v>
+      <c r="A96" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Short Proceeds 做空收入</t>
+        </is>
+      </c>
+      <c r="B96" s="13" t="n">
+        <v>720586.41</v>
+      </c>
+      <c r="C96" s="13" t="n">
+        <v>734929.42</v>
+      </c>
+      <c r="D96" s="13" t="n">
+        <v>801276.66</v>
+      </c>
+      <c r="E96" s="13" t="n">
+        <v>697139.47</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="12" t="inlineStr">
-        <is>
-          <t>Short Book — Short Proceeds 做空收入</t>
-        </is>
-      </c>
-      <c r="B97" s="13" t="n">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>Short Book — Market Value 市值(负债)</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="n">
         <v>720586.41</v>
       </c>
-      <c r="C97" s="13" t="n">
+      <c r="C97" s="4" t="n">
         <v>734929.42</v>
       </c>
-      <c r="D97" s="13" t="n">
+      <c r="D97" s="4" t="n">
         <v>801276.66</v>
       </c>
-      <c r="E97" s="13" t="n">
+      <c r="E97" s="4" t="n">
         <v>697139.47</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="10" t="inlineStr">
-        <is>
-          <t>Short Book — Market Value 市值(负债)</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="n">
-        <v>720586.41</v>
-      </c>
-      <c r="C98" s="4" t="n">
-        <v>734929.42</v>
-      </c>
-      <c r="D98" s="4" t="n">
-        <v>801276.66</v>
-      </c>
-      <c r="E98" s="4" t="n">
-        <v>697139.47</v>
+      <c r="A98" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Margin Loan 融资(2%)</t>
+        </is>
+      </c>
+      <c r="B98" s="13" t="n">
+        <v>14411.73</v>
+      </c>
+      <c r="C98" s="13" t="n">
+        <v>14698.59</v>
+      </c>
+      <c r="D98" s="13" t="n">
+        <v>16025.53</v>
+      </c>
+      <c r="E98" s="13" t="n">
+        <v>13942.79</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="14" t="inlineStr">
+      <c r="A99" s="16" t="inlineStr">
         <is>
           <t>Short Book — NAV</t>
         </is>
       </c>
-      <c r="B99" s="13" t="n">
-        <v>132436.48</v>
-      </c>
-      <c r="C99" s="13" t="n">
-        <v>156279.94</v>
-      </c>
-      <c r="D99" s="13" t="n">
-        <v>150915.95</v>
-      </c>
-      <c r="E99" s="13" t="n">
-        <v>235430.77</v>
+      <c r="B99" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="10" t="inlineStr">
+      <c r="A100" s="12" t="inlineStr">
         <is>
           <t>Unallocated Cash 未分配现金</t>
         </is>
       </c>
-      <c r="B100" s="11" t="n">
+      <c r="B100" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="15" t="n">
         <v>-0</v>
       </c>
-      <c r="C100" s="11" t="n">
+      <c r="D100" s="15" t="n">
         <v>-0</v>
       </c>
-      <c r="D100" s="11" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E100" s="11" t="n">
+      <c r="E100" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="14" t="inlineStr">
+      <c r="A101" s="16" t="inlineStr">
         <is>
           <t>Dual-View NAV 双账户法NAV</t>
         </is>
       </c>
-      <c r="B101" s="13" t="n">
-        <v>433995.13</v>
-      </c>
-      <c r="C101" s="13" t="n">
-        <v>532378.24</v>
-      </c>
-      <c r="D101" s="13" t="n">
-        <v>411262.04</v>
-      </c>
-      <c r="E101" s="13" t="n">
-        <v>426209.33</v>
+      <c r="B101" s="4" t="n">
+        <v>436927.53</v>
+      </c>
+      <c r="C101" s="4" t="n">
+        <v>535975.39</v>
+      </c>
+      <c r="D101" s="4" t="n">
+        <v>414040.84</v>
+      </c>
+      <c r="E101" s="4" t="n">
+        <v>429089.12</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="10" t="inlineStr">
+      <c r="A102" s="12" t="inlineStr">
         <is>
           <t>NAV Alignment Check (≈0)</t>
         </is>
       </c>
-      <c r="B102" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C102" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" s="7" t="n">
+      <c r="B102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6728,22 +6728,22 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Net income</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n">
-        <v>-103820.68</v>
+      <c r="B5" s="19" t="n">
+        <v>-104456.09</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>17727.69</v>
-      </c>
-      <c r="D5" s="18" t="n">
-        <v>-32715.89</v>
+        <v>17908.29</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>-32444.75</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>85918.46000000001</v>
+        <v>85756.85000000001</v>
       </c>
     </row>
     <row r="6">
@@ -6752,17 +6752,17 @@
           <t>Interest expense (est)</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
-        <v>98.48999999999999</v>
+      <c r="B6" s="13" t="n">
+        <v>100.73</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>492.45</v>
+        <v>503.64</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>2068.28</v>
+        <v>2115.27</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>14674.94</v>
+        <v>15008.37</v>
       </c>
     </row>
     <row r="7">
@@ -6810,22 +6810,22 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Net income</t>
         </is>
       </c>
-      <c r="B11" s="18" t="n">
-        <v>-5437.57</v>
-      </c>
-      <c r="C11" s="18" t="n">
-        <v>-5005.4</v>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>-40501.69</v>
+      <c r="B11" s="19" t="n">
+        <v>-5408.23</v>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>-4978.39</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>-40283.15</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>64090.18</v>
+        <v>60996.18</v>
       </c>
     </row>
     <row r="12">
@@ -6834,16 +6834,16 @@
           <t>Interest expense (est)</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="17" t="n">
+      <c r="B12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
           <t>Current unrealized PnL</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
         <v>-1479.68</v>
       </c>
     </row>
@@ -6892,22 +6892,22 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Net income</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n">
-        <v>-98383.11</v>
+      <c r="B17" s="19" t="n">
+        <v>-99047.86</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>22733.09</v>
+        <v>22886.69</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>7785.8</v>
+        <v>7838.41</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>21828.28</v>
+        <v>24760.68</v>
       </c>
     </row>
     <row r="18">
@@ -6917,16 +6917,16 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>165.31</v>
+        <v>166.89</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>826.5599999999999</v>
+        <v>834.4299999999999</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>3471.57</v>
+        <v>3504.59</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>24631.63</v>
+        <v>24865.93</v>
       </c>
     </row>
     <row r="19">
@@ -7012,19 +7012,19 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Beginning NAV</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1111237.93</v>
+        <v>1111711.73</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>989689.5600000001</v>
+        <v>989347.35</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1040133.14</v>
+        <v>1039700.39</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>921498.79</v>
@@ -7036,17 +7036,17 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
-        <v>-103820.68</v>
+      <c r="B6" s="18" t="n">
+        <v>-104456.09</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>17727.69</v>
-      </c>
-      <c r="D6" s="19" t="n">
-        <v>-32715.89</v>
+        <v>17908.29</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>-32444.75</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>85918.46000000001</v>
+        <v>85756.85000000001</v>
       </c>
     </row>
     <row r="7">
@@ -7074,36 +7074,36 @@
           <t>Withdrawals</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="17" t="n">
+      <c r="B8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Ending NAV</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1007417.25</v>
+        <v>1007255.64</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1007417.25</v>
+        <v>1007255.64</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1007417.25</v>
+        <v>1007255.64</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1007417.25</v>
+        <v>1007255.64</v>
       </c>
     </row>
     <row r="10">
@@ -7113,16 +7113,16 @@
         </is>
       </c>
       <c r="B10" s="20" t="n">
-        <v>-9.34</v>
+        <v>-9.4</v>
       </c>
       <c r="C10" s="21" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="D10" s="20" t="n">
-        <v>-3.15</v>
+        <v>-3.12</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>9.32</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="11">
@@ -7132,16 +7132,16 @@
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>-9.34</v>
+        <v>-9.4</v>
       </c>
       <c r="C11" s="22" t="n">
-        <v>-9.34</v>
+        <v>-9.4</v>
       </c>
       <c r="D11" s="22" t="n">
-        <v>-9.34</v>
+        <v>-9.4</v>
       </c>
       <c r="E11" s="22" t="n">
-        <v>-9.460000000000001</v>
+        <v>-9.470000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -7179,19 +7179,19 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Beginning NAV</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>578859.6899999999</v>
+        <v>575736.35</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>578427.52</v>
+        <v>575306.51</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>613923.8100000001</v>
+        <v>610611.27</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>509331.94</v>
@@ -7203,17 +7203,17 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="B16" s="19" t="n">
-        <v>-5437.57</v>
-      </c>
-      <c r="C16" s="19" t="n">
-        <v>-5005.4</v>
-      </c>
-      <c r="D16" s="19" t="n">
-        <v>-40501.69</v>
+      <c r="B16" s="18" t="n">
+        <v>-5408.23</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>-4978.39</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>-40283.15</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>64090.18</v>
+        <v>60996.18</v>
       </c>
     </row>
     <row r="17">
@@ -7241,36 +7241,36 @@
           <t>Withdrawals</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="17" t="n">
+      <c r="B18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Ending NAV</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>573422.12</v>
+        <v>570328.12</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>573422.12</v>
+        <v>570328.12</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>573422.12</v>
+        <v>570328.12</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>573422.12</v>
+        <v>570328.12</v>
       </c>
     </row>
     <row r="20">
@@ -7289,7 +7289,7 @@
         <v>-6.6</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>12.58</v>
+        <v>11.98</v>
       </c>
     </row>
     <row r="21">
@@ -7346,19 +7346,19 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Beginning NAV</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>532378.24</v>
+        <v>535975.39</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>411262.04</v>
+        <v>414040.84</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>426209.33</v>
+        <v>429089.12</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>412166.85</v>
@@ -7370,17 +7370,17 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="B26" s="19" t="n">
-        <v>-98383.11</v>
+      <c r="B26" s="18" t="n">
+        <v>-99047.86</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>22733.09</v>
+        <v>22886.69</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>7785.8</v>
+        <v>7838.41</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>21828.28</v>
+        <v>24760.68</v>
       </c>
     </row>
     <row r="27">
@@ -7408,36 +7408,36 @@
           <t>Withdrawals</t>
         </is>
       </c>
-      <c r="B28" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="17" t="n">
+      <c r="B28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Ending NAV</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>433995.13</v>
+        <v>436927.53</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>433995.13</v>
+        <v>436927.53</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>433995.13</v>
+        <v>436927.53</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>433995.13</v>
+        <v>436927.53</v>
       </c>
     </row>
     <row r="30">
@@ -7456,7 +7456,7 @@
         <v>1.83</v>
       </c>
       <c r="E30" s="21" t="n">
-        <v>5.3</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="31">
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>17727.69</v>
+        <v>17908.29</v>
       </c>
     </row>
     <row r="5">
@@ -7534,7 +7534,7 @@
           <t>Investing cash flow</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="19" t="n">
         <v>-332849.58</v>
       </c>
     </row>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>174347.43</v>
+        <v>171351.35</v>
       </c>
     </row>
     <row r="7">
@@ -7554,8 +7554,8 @@
           <t>Net change in cash</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
-        <v>-140774.46</v>
+      <c r="B7" s="19" t="n">
+        <v>-143589.94</v>
       </c>
     </row>
     <row r="8">
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="B96" s="4" t="n">
-        <v>1011267.7</v>
+        <v>1011218.51</v>
       </c>
     </row>
     <row r="97">
@@ -8562,7 +8562,7 @@
         </is>
       </c>
       <c r="B97" s="13" t="n">
-        <v>1025559.43</v>
+        <v>1025407</v>
       </c>
     </row>
     <row r="98">
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="B98" s="4" t="n">
-        <v>1027048.7</v>
+        <v>1026941.31</v>
       </c>
     </row>
     <row r="99">
@@ -8582,7 +8582,7 @@
         </is>
       </c>
       <c r="B99" s="13" t="n">
-        <v>1015215.52</v>
+        <v>1015258.85</v>
       </c>
     </row>
     <row r="100">
@@ -8592,7 +8592,7 @@
         </is>
       </c>
       <c r="B100" s="4" t="n">
-        <v>1002934.71</v>
+        <v>1003003.03</v>
       </c>
     </row>
     <row r="101">
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="B101" s="13" t="n">
-        <v>1012978.6</v>
+        <v>1013068.4</v>
       </c>
     </row>
     <row r="102">
@@ -8612,7 +8612,7 @@
         </is>
       </c>
       <c r="B102" s="4" t="n">
-        <v>1026516.54</v>
+        <v>1026667.89</v>
       </c>
     </row>
     <row r="103">
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="B103" s="13" t="n">
-        <v>1053076.18</v>
+        <v>1053397.75</v>
       </c>
     </row>
     <row r="104">
@@ -8632,7 +8632,7 @@
         </is>
       </c>
       <c r="B104" s="4" t="n">
-        <v>1050409.43</v>
+        <v>1050736.08</v>
       </c>
     </row>
     <row r="105">
@@ -8642,7 +8642,7 @@
         </is>
       </c>
       <c r="B105" s="13" t="n">
-        <v>1049250.56</v>
+        <v>1049499.07</v>
       </c>
     </row>
     <row r="106">
@@ -8652,7 +8652,7 @@
         </is>
       </c>
       <c r="B106" s="4" t="n">
-        <v>1048939.07</v>
+        <v>1049134.93</v>
       </c>
     </row>
     <row r="107">
@@ -8662,7 +8662,7 @@
         </is>
       </c>
       <c r="B107" s="13" t="n">
-        <v>1042782.27</v>
+        <v>1042919.9</v>
       </c>
     </row>
     <row r="108">
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="B108" s="4" t="n">
-        <v>1048540.41</v>
+        <v>1048685.92</v>
       </c>
     </row>
     <row r="109">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="B109" s="13" t="n">
-        <v>1042626.09</v>
+        <v>1042773.4</v>
       </c>
     </row>
     <row r="110">
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="B110" s="4" t="n">
-        <v>1044064.62</v>
+        <v>1044235.83</v>
       </c>
     </row>
     <row r="111">
@@ -8702,7 +8702,7 @@
         </is>
       </c>
       <c r="B111" s="13" t="n">
-        <v>1070190.07</v>
+        <v>1070354.14</v>
       </c>
     </row>
     <row r="112">
@@ -8712,7 +8712,7 @@
         </is>
       </c>
       <c r="B112" s="4" t="n">
-        <v>1061381.1</v>
+        <v>1061514.84</v>
       </c>
     </row>
     <row r="113">
@@ -8722,7 +8722,7 @@
         </is>
       </c>
       <c r="B113" s="13" t="n">
-        <v>1074843.71</v>
+        <v>1074870.62</v>
       </c>
     </row>
     <row r="114">
@@ -8732,7 +8732,7 @@
         </is>
       </c>
       <c r="B114" s="4" t="n">
-        <v>1080539.46</v>
+        <v>1080512.52</v>
       </c>
     </row>
     <row r="115">
@@ -8742,7 +8742,7 @@
         </is>
       </c>
       <c r="B115" s="13" t="n">
-        <v>1087013.93</v>
+        <v>1086924.48</v>
       </c>
     </row>
     <row r="116">
@@ -8752,7 +8752,7 @@
         </is>
       </c>
       <c r="B116" s="4" t="n">
-        <v>1071732.17</v>
+        <v>1071780.32</v>
       </c>
     </row>
     <row r="117">
@@ -8762,7 +8762,7 @@
         </is>
       </c>
       <c r="B117" s="13" t="n">
-        <v>1065536.29</v>
+        <v>1065526.09</v>
       </c>
     </row>
     <row r="118">
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="B118" s="4" t="n">
-        <v>1080686.27</v>
+        <v>1080594.32</v>
       </c>
     </row>
     <row r="119">
@@ -8782,7 +8782,7 @@
         </is>
       </c>
       <c r="B119" s="13" t="n">
-        <v>1075745.66</v>
+        <v>1075591.99</v>
       </c>
     </row>
     <row r="120">
@@ -8792,7 +8792,7 @@
         </is>
       </c>
       <c r="B120" s="4" t="n">
-        <v>1071198.07</v>
+        <v>1071013.67</v>
       </c>
     </row>
     <row r="121">
@@ -8802,7 +8802,7 @@
         </is>
       </c>
       <c r="B121" s="13" t="n">
-        <v>1073921.38</v>
+        <v>1073689.47</v>
       </c>
     </row>
     <row r="122">
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="B122" s="4" t="n">
-        <v>1074464.87</v>
+        <v>1074236.64</v>
       </c>
     </row>
     <row r="123">
@@ -8822,7 +8822,7 @@
         </is>
       </c>
       <c r="B123" s="13" t="n">
-        <v>1084806.36</v>
+        <v>1084547.15</v>
       </c>
     </row>
     <row r="124">
@@ -8832,7 +8832,7 @@
         </is>
       </c>
       <c r="B124" s="4" t="n">
-        <v>1085780.99</v>
+        <v>1085528.37</v>
       </c>
     </row>
     <row r="125">
@@ -8842,7 +8842,7 @@
         </is>
       </c>
       <c r="B125" s="13" t="n">
-        <v>1092869.82</v>
+        <v>1092616.33</v>
       </c>
     </row>
     <row r="126">
@@ -8852,7 +8852,7 @@
         </is>
       </c>
       <c r="B126" s="4" t="n">
-        <v>1093051.87</v>
+        <v>1092781.06</v>
       </c>
     </row>
     <row r="127">
@@ -8862,7 +8862,7 @@
         </is>
       </c>
       <c r="B127" s="13" t="n">
-        <v>1053872.36</v>
+        <v>1053336.82</v>
       </c>
     </row>
     <row r="128">
@@ -8872,7 +8872,7 @@
         </is>
       </c>
       <c r="B128" s="4" t="n">
-        <v>1050211.4</v>
+        <v>1049687.33</v>
       </c>
     </row>
     <row r="129">
@@ -8882,7 +8882,7 @@
         </is>
       </c>
       <c r="B129" s="13" t="n">
-        <v>1044592.3</v>
+        <v>1044100.12</v>
       </c>
     </row>
     <row r="130">
@@ -8892,7 +8892,7 @@
         </is>
       </c>
       <c r="B130" s="4" t="n">
-        <v>1033089.1</v>
+        <v>1032626.83</v>
       </c>
     </row>
     <row r="131">
@@ -8902,7 +8902,7 @@
         </is>
       </c>
       <c r="B131" s="13" t="n">
-        <v>1040133.14</v>
+        <v>1039700.39</v>
       </c>
     </row>
     <row r="132">
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="B132" s="4" t="n">
-        <v>1037961.39</v>
+        <v>1037551.62</v>
       </c>
     </row>
     <row r="133">
@@ -8922,7 +8922,7 @@
         </is>
       </c>
       <c r="B133" s="13" t="n">
-        <v>1019662.98</v>
+        <v>1019311.74</v>
       </c>
     </row>
     <row r="134">
@@ -8932,7 +8932,7 @@
         </is>
       </c>
       <c r="B134" s="4" t="n">
-        <v>1014448.4</v>
+        <v>1014163.76</v>
       </c>
     </row>
     <row r="135">
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="B135" s="13" t="n">
-        <v>999507.12</v>
+        <v>999293.04</v>
       </c>
     </row>
     <row r="136">
@@ -8952,7 +8952,7 @@
         </is>
       </c>
       <c r="B136" s="4" t="n">
-        <v>1011705.6</v>
+        <v>1011409.78</v>
       </c>
     </row>
     <row r="137">
@@ -8962,7 +8962,7 @@
         </is>
       </c>
       <c r="B137" s="13" t="n">
-        <v>1014861.55</v>
+        <v>1014540.8</v>
       </c>
     </row>
     <row r="138">
@@ -8972,7 +8972,7 @@
         </is>
       </c>
       <c r="B138" s="4" t="n">
-        <v>1012199.68</v>
+        <v>1011881.11</v>
       </c>
     </row>
     <row r="139">
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="B139" s="13" t="n">
-        <v>998700.78</v>
+        <v>998415.39</v>
       </c>
     </row>
     <row r="140">
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B140" s="4" t="n">
-        <v>1014531.63</v>
+        <v>1014351.76</v>
       </c>
     </row>
     <row r="141">
@@ -9002,7 +9002,7 @@
         </is>
       </c>
       <c r="B141" s="13" t="n">
-        <v>1023703.62</v>
+        <v>1023498.77</v>
       </c>
     </row>
     <row r="142">
@@ -9012,7 +9012,7 @@
         </is>
       </c>
       <c r="B142" s="4" t="n">
-        <v>1023844.85</v>
+        <v>1023696.66</v>
       </c>
     </row>
     <row r="143">
@@ -9022,7 +9022,7 @@
         </is>
       </c>
       <c r="B143" s="13" t="n">
-        <v>997176.6800000001</v>
+        <v>996887.45</v>
       </c>
     </row>
     <row r="144">
@@ -9032,7 +9032,7 @@
         </is>
       </c>
       <c r="B144" s="4" t="n">
-        <v>1016658.53</v>
+        <v>1016573.57</v>
       </c>
     </row>
     <row r="145">
@@ -9042,7 +9042,7 @@
         </is>
       </c>
       <c r="B145" s="13" t="n">
-        <v>998042.9300000001</v>
+        <v>997861.24</v>
       </c>
     </row>
     <row r="146">
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="B146" s="4" t="n">
-        <v>991773.6899999999</v>
+        <v>991493.7</v>
       </c>
     </row>
     <row r="147">
@@ -9062,7 +9062,7 @@
         </is>
       </c>
       <c r="B147" s="13" t="n">
-        <v>989689.5600000001</v>
+        <v>989347.35</v>
       </c>
     </row>
     <row r="148">
@@ -9072,7 +9072,7 @@
         </is>
       </c>
       <c r="B148" s="4" t="n">
-        <v>1005172.26</v>
+        <v>1004898.62</v>
       </c>
     </row>
     <row r="149">
@@ -9082,7 +9082,7 @@
         </is>
       </c>
       <c r="B149" s="13" t="n">
-        <v>1099286.25</v>
+        <v>1099657.36</v>
       </c>
     </row>
     <row r="150">
@@ -9092,7 +9092,7 @@
         </is>
       </c>
       <c r="B150" s="4" t="n">
-        <v>1107994.97</v>
+        <v>1108417.28</v>
       </c>
     </row>
     <row r="151">
@@ -9102,7 +9102,7 @@
         </is>
       </c>
       <c r="B151" s="13" t="n">
-        <v>1111237.93</v>
+        <v>1111711.73</v>
       </c>
     </row>
     <row r="152">
@@ -9112,7 +9112,7 @@
         </is>
       </c>
       <c r="B152" s="4" t="n">
-        <v>1007417.25</v>
+        <v>1007255.64</v>
       </c>
     </row>
   </sheetData>
@@ -9217,7 +9217,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1007417.25</v>
+        <v>1007255.64</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>1726390.64</v>
@@ -9232,16 +9232,16 @@
         <v>917658.83</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>2.516</v>
+        <v>2.517</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>0.911</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>251.65</v>
+        <v>251.69</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>125.82</v>
+        <v>125.84</v>
       </c>
       <c r="K4" s="23" t="n">
         <v>14</v>
@@ -9254,7 +9254,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>573422.12</v>
+        <v>570328.12</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>85611.06</v>
@@ -9265,20 +9265,20 @@
       <c r="E5" s="13" t="n">
         <v>173756.46</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="18" t="n">
         <v>-2534.34</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>0.303</v>
+        <v>0.305</v>
       </c>
       <c r="H5" s="24" t="n">
         <v>-0.004</v>
       </c>
       <c r="I5" s="24" t="n">
-        <v>30.3</v>
+        <v>30.47</v>
       </c>
       <c r="J5" s="24" t="n">
-        <v>15.15</v>
+        <v>15.23</v>
       </c>
       <c r="K5" s="25" t="n">
         <v>1</v>
@@ -9291,7 +9291,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>433995.13</v>
+        <v>436927.53</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>1640779.58</v>
@@ -9306,16 +9306,16 @@
         <v>920193.17</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>5.441</v>
+        <v>5.404</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>2.12</v>
+        <v>2.106</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>544.1</v>
+        <v>540.45</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>272.05</v>
+        <v>270.22</v>
       </c>
       <c r="K6" s="23" t="n">
         <v>13</v>
@@ -9405,7 +9405,7 @@
         <v>342668.34</v>
       </c>
       <c r="D6" s="27" t="n">
-        <v>34.01</v>
+        <v>34.02</v>
       </c>
       <c r="E6" s="27" t="n">
         <v>13.52</v>
@@ -9471,7 +9471,7 @@
         <v>221871.36</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>22.02</v>
+        <v>22.03</v>
       </c>
       <c r="E9" s="21" t="n">
         <v>8.75</v>
@@ -9493,7 +9493,7 @@
         <v>210282.8</v>
       </c>
       <c r="D10" s="27" t="n">
-        <v>20.87</v>
+        <v>20.88</v>
       </c>
       <c r="E10" s="27" t="n">
         <v>8.289999999999999</v>
@@ -9515,7 +9515,7 @@
         <v>167567.1</v>
       </c>
       <c r="D11" s="21" t="n">
-        <v>16.63</v>
+        <v>16.64</v>
       </c>
       <c r="E11" s="21" t="n">
         <v>6.61</v>
@@ -9555,7 +9555,7 @@
       <c r="B13" s="13" t="n">
         <v>139917.3</v>
       </c>
-      <c r="C13" s="19" t="n">
+      <c r="C13" s="18" t="n">
         <v>-139917.3</v>
       </c>
       <c r="D13" s="21" t="n">
@@ -9577,7 +9577,7 @@
       <c r="B14" s="4" t="n">
         <v>88145.39999999999</v>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>-88145.39999999999</v>
       </c>
       <c r="D14" s="27" t="n">
@@ -9671,16 +9671,16 @@
           <t>health</t>
         </is>
       </c>
-      <c r="B21" s="17" t="n">
+      <c r="B21" s="15" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>471861.66</v>
       </c>
-      <c r="D21" s="19" t="n">
+      <c r="D21" s="18" t="n">
         <v>-471861.66</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>-18.61</v>
       </c>
     </row>
@@ -9718,7 +9718,7 @@
       <c r="D23" s="13" t="n">
         <v>290507.22</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>11.46</v>
       </c>
     </row>
@@ -9734,7 +9734,7 @@
       <c r="C24" s="4" t="n">
         <v>76705.2</v>
       </c>
-      <c r="D24" s="18" t="n">
+      <c r="D24" s="19" t="n">
         <v>-76705.2</v>
       </c>
       <c r="E24" s="7" t="n">
@@ -9753,10 +9753,10 @@
       <c r="C25" s="13" t="n">
         <v>134325.05</v>
       </c>
-      <c r="D25" s="19" t="n">
+      <c r="D25" s="18" t="n">
         <v>-48713.99</v>
       </c>
-      <c r="E25" s="16" t="n">
+      <c r="E25" s="17" t="n">
         <v>-1.92</v>
       </c>
     </row>
@@ -9805,7 +9805,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>2.49</v>
+        <v>2.491</v>
       </c>
     </row>
     <row r="5">
@@ -9815,7 +9815,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>91.34</v>
+        <v>91.36</v>
       </c>
     </row>
     <row r="6">

--- a/trading_signals/risk_management/risk_workbook_20260606_031417.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260606_031417.xlsx
@@ -728,7 +728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-05  ·  Generated 2026-06-10T09:47:46  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-05  ·  Generated 2026-06-24T18:50:34  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1007255.64</v>
+        <v>1007201.77</v>
       </c>
     </row>
     <row r="5">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>2.517</v>
+        <v>4.396</v>
       </c>
     </row>
     <row r="6">
@@ -758,8 +758,8 @@
           <t>Net leverage (x)</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>0.911</v>
+      <c r="B6" s="5" t="n">
+        <v>2.79</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1.893</v>
+        <v>6.257</v>
       </c>
     </row>
     <row r="8">
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>41670.94</v>
+        <v>127447.75</v>
       </c>
     </row>
     <row r="9">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>4.14</v>
+        <v>12.65</v>
       </c>
     </row>
     <row r="10">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>39.92</v>
+        <v>122.11</v>
       </c>
     </row>
     <row r="11">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.729</v>
       </c>
     </row>
     <row r="13">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>8.85</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -840,7 +840,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>2.69 / 1.35</t>
+          <t>2.68 / 1.34</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>2.517</v>
+        <v>4.396</v>
       </c>
     </row>
     <row r="16">
@@ -862,7 +862,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>BWA (34.02% NAV)</t>
+          <t>KLAC (208.78% NAV)</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>31.06</v>
+        <v>60.53</v>
       </c>
     </row>
     <row r="18">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>41670.94</v>
+        <v>127447.75</v>
       </c>
     </row>
     <row r="4">
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>58921.95</v>
+        <v>180208.79</v>
       </c>
     </row>
     <row r="5">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>402131.08</v>
+        <v>1229890.77</v>
       </c>
     </row>
     <row r="6">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>39.92</v>
+        <v>122.11</v>
       </c>
     </row>
     <row r="7">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>21335.46</v>
+        <v>87294.89999999999</v>
       </c>
     </row>
     <row r="8">
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>47624.33</v>
+        <v>155333.59</v>
       </c>
     </row>
     <row r="10">
@@ -1024,105 +1024,105 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>LRCX/BSX</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>6378.93</v>
+        <v>61009.47</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>15.31</v>
+        <v>47.87</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>LRCX/RMD</t>
+          <t>KLAC/LOW</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>5558.93</v>
+        <v>37861.22</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>13.34</v>
+        <v>29.71</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>LRCX/BSX</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>5083.22</v>
+        <v>6329.41</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>12.2</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>KLAC/LOW</t>
+          <t>LRCX/RMD</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>3082.96</v>
+        <v>5710.59</v>
       </c>
       <c r="C15" s="17" t="n">
-        <v>7.4</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>STLD/HII</t>
+          <t>BWA/CME</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2977.49</v>
+        <v>2451.12</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>7.15</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>STLD/ISRG</t>
+          <t>CSCO/CAG</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>2820.38</v>
+        <v>2119.47</v>
       </c>
       <c r="C17" s="17" t="n">
-        <v>6.77</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>CSCO/CAG</t>
+          <t>STLD/HII</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>2769.55</v>
+        <v>2086.97</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>6.65</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>BWA/CME</t>
+          <t>STLD/ISRG</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>2644.94</v>
+        <v>2086.05</v>
       </c>
       <c r="C19" s="17" t="n">
-        <v>6.35</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="20">
@@ -1132,36 +1132,36 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2397.98</v>
+        <v>1760.83</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>5.75</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>CSCO/REGN</t>
+          <t>BWA/VLTO</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>2213.83</v>
+        <v>1665.95</v>
       </c>
       <c r="C21" s="17" t="n">
-        <v>5.31</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>BWA/VLTO</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>2112.88</v>
+        <v>1562.69</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>5.07</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="23">
@@ -1171,23 +1171,23 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1767.25</v>
+        <v>1422.2</v>
       </c>
       <c r="C23" s="17" t="n">
-        <v>4.24</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>CSCO/REGN</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>1728.04</v>
+        <v>1331.04</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>4.15</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="25">
@@ -1196,11 +1196,11 @@
           <t>HAS/PFE</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n">
-        <v>134.56</v>
+      <c r="B25" s="15" t="n">
+        <v>50.74</v>
       </c>
       <c r="C25" s="17" t="n">
-        <v>0.32</v>
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>
@@ -1321,8 +1321,8 @@
           <t>KLAC/REGN</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n">
-        <v>67</v>
+      <c r="C8" s="4" t="n">
+        <v>670</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>1020220</v>
@@ -1363,8 +1363,8 @@
           <t>KLAC/LOW</t>
         </is>
       </c>
-      <c r="C10" s="11" t="n">
-        <v>42</v>
+      <c r="C10" s="4" t="n">
+        <v>420</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>1020220</v>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>-95336.75</v>
+        <v>-315103.07</v>
       </c>
       <c r="C4" s="22" t="n">
-        <v>-9.470000000000001</v>
+        <v>-31.29</v>
       </c>
     </row>
     <row r="5">
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>-190673.49</v>
+        <v>-630206.15</v>
       </c>
       <c r="C5" s="20" t="n">
-        <v>-18.93</v>
+        <v>-62.57</v>
       </c>
     </row>
     <row r="6">
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>-95336.75</v>
+        <v>-315103.07</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>-9.470000000000001</v>
+        <v>-31.29</v>
       </c>
     </row>
     <row r="7">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="B7" s="18" t="n">
-        <v>-78746.98</v>
+        <v>-268001.5</v>
       </c>
       <c r="C7" s="20" t="n">
-        <v>-7.82</v>
+        <v>-26.61</v>
       </c>
     </row>
   </sheetData>
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>5.4</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="D6" s="32" t="n">
         <v>3</v>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>2.11</v>
+        <v>6.42</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>0.5</v>
@@ -1857,11 +1857,11 @@
       </c>
       <c r="B8" s="32" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>34.02</v>
+        <v>208.78</v>
       </c>
       <c r="D8" s="32" t="n">
         <v>15</v>
@@ -1883,11 +1883,11 @@
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>26.76</v>
+        <v>34.02</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>15</v>
@@ -1909,11 +1909,11 @@
       </c>
       <c r="B10" s="32" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>25.95</v>
+        <v>26.76</v>
       </c>
       <c r="D10" s="32" t="n">
         <v>15</v>
@@ -1928,54 +1928,54 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>sector_net</t>
         </is>
       </c>
-      <c r="B11" s="34" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="C11" s="34" t="n">
-        <v>31.06</v>
-      </c>
-      <c r="D11" s="34" t="n">
+      <c r="C11" s="32" t="n">
+        <v>60.53</v>
+      </c>
+      <c r="D11" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="E11" s="34" t="n">
+      <c r="E11" s="32" t="n">
         <v>50</v>
       </c>
-      <c r="F11" s="34" t="inlineStr">
+      <c r="F11" s="32" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>max_pair</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="C12" s="34" t="n">
+        <v>29.52</v>
+      </c>
+      <c r="D12" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="E12" s="34" t="n">
+        <v>35</v>
+      </c>
+      <c r="F12" s="34" t="inlineStr">
         <is>
           <t>amber</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="29" t="inlineStr">
-        <is>
-          <t>max_pair</t>
-        </is>
-      </c>
-      <c r="B12" s="30" t="inlineStr">
-        <is>
-          <t>combined</t>
-        </is>
-      </c>
-      <c r="C12" s="30" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="D12" s="30" t="n">
-        <v>20</v>
-      </c>
-      <c r="E12" s="30" t="n">
-        <v>35</v>
-      </c>
-      <c r="F12" s="30" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>1.89</v>
+        <v>6.26</v>
       </c>
       <c r="D13" s="32" t="n">
         <v>0.3</v>
@@ -2006,28 +2006,28 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>var_95_1d</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>combined</t>
         </is>
       </c>
-      <c r="C14" s="34" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="D14" s="34" t="n">
+      <c r="C14" s="32" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="D14" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="34" t="n">
+      <c r="E14" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="F14" s="34" t="inlineStr">
-        <is>
-          <t>amber</t>
+      <c r="F14" s="32" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
     </row>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="E6" s="25" t="n">
-        <v>67</v>
+        <v>670</v>
       </c>
       <c r="F6" s="13" t="n">
         <v>1929.2</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>129256.4</v>
+        <v>1292564</v>
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
@@ -2365,13 +2365,13 @@
         </is>
       </c>
       <c r="E8" s="25" t="n">
-        <v>42</v>
+        <v>420</v>
       </c>
       <c r="F8" s="13" t="n">
         <v>1929.2</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>81026.39999999999</v>
+        <v>810264</v>
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
@@ -3511,11 +3511,11 @@
           <t>KLAC/REGN</t>
         </is>
       </c>
-      <c r="C5" s="19" t="n">
-        <v>-5525.82</v>
+      <c r="C5" s="4" t="n">
+        <v>1157781.78</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>143871.75</v>
+        <v>1307179.35</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>2808.7</v>
+        <v>732046.3</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>161529.08</v>
+        <v>890766.6800000001</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>1</v>
@@ -4096,16 +4096,16 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>15.43</v>
+        <v>15.76</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>0.24</v>
+        <v>0.59</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>25</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>-15.19</v>
+        <v>-15.17</v>
       </c>
     </row>
     <row r="7">
@@ -4115,16 +4115,16 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>11.82</v>
+        <v>12.12</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>16.03</v>
+        <v>19.9</v>
       </c>
       <c r="D7" s="17" t="n">
         <v>25</v>
       </c>
       <c r="E7" s="21" t="n">
-        <v>4.21</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="8">
@@ -4134,16 +4134,16 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>26.02</v>
+        <v>26.61</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>4.06</v>
+        <v>4.75</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>-21.96</v>
+        <v>-21.86</v>
       </c>
     </row>
     <row r="9">
@@ -4153,16 +4153,16 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>46.73</v>
+        <v>45.5</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>79.67</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="D9" s="17" t="n">
         <v>25</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>32.93</v>
+        <v>29.26</v>
       </c>
     </row>
     <row r="11">
@@ -4187,81 +4187,81 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>LRCX/BSX</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>15.31</v>
+        <v>47.87</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>LRCX/RMD</t>
+          <t>KLAC/LOW</t>
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>13.34</v>
+        <v>29.71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>LRCX/BSX</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>12.2</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>KLAC/LOW</t>
+          <t>LRCX/RMD</t>
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>7.4</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>STLD/HII</t>
+          <t>BWA/CME</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>7.15</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>STLD/ISRG</t>
+          <t>CSCO/CAG</t>
         </is>
       </c>
       <c r="B18" s="17" t="n">
-        <v>6.77</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>CSCO/CAG</t>
+          <t>STLD/ISRG</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>6.65</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>BWA/CME</t>
+          <t>STLD/HII</t>
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>6.35</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="21">
@@ -4271,27 +4271,27 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>5.75</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>CSCO/REGN</t>
+          <t>BWA/VLTO</t>
         </is>
       </c>
       <c r="B22" s="17" t="n">
-        <v>5.31</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>BWA/VLTO</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>5.07</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="24">
@@ -4301,17 +4301,17 @@
         </is>
       </c>
       <c r="B24" s="17" t="n">
-        <v>4.24</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>CSCO/REGN</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>4.15</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="26">
@@ -4321,7 +4321,7 @@
         </is>
       </c>
       <c r="B26" s="17" t="n">
-        <v>0.32</v>
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="B5" s="27" t="n">
-        <v>38.97</v>
+        <v>38.94</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>2.6</v>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>-0.111 (t=-0.62)</t>
+          <t>-0.11 (t=-0.62)</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>48.07</v>
+        <v>47.74</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="D6" s="17" t="n">
         <v>0.059</v>
@@ -4494,27 +4494,27 @@
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>0.056 (t=0.39)</t>
+          <t>0.059 (t=0.41)</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>-0.116 (t=-0.52)</t>
+          <t>-0.119 (t=-0.54)</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>-0.06 (t=-0.31)</t>
+          <t>-0.059 (t=-0.3)</t>
         </is>
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
-          <t>0.241 (t=1.31)</t>
+          <t>0.244 (t=1.32)</t>
         </is>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t>-0.207 (t=-0.72)</t>
+          <t>-0.208 (t=-0.72)</t>
         </is>
       </c>
       <c r="K6" s="17" t="inlineStr">
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>28.62</v>
+        <v>29.07</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>1.03</v>
@@ -4543,32 +4543,32 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>-0.069 (t=-0.42)</t>
+          <t>-0.073 (t=-0.44)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>-0.004 (t=-0.02)</t>
+          <t>0.001 (t=0.0)</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>0.235 (t=1.04)</t>
+          <t>0.234 (t=1.03)</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>-0.103 (t=-0.49)</t>
+          <t>-0.106 (t=-0.5)</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>0.022 (t=0.07)</t>
+          <t>0.023 (t=0.07)</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>-0.065 (t=-0.55)</t>
+          <t>-0.064 (t=-0.53)</t>
         </is>
       </c>
     </row>
@@ -4657,10 +4657,10 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>-0.186</v>
+        <v>-0.183</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>29.655</v>
+        <v>29.721</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>0</v>
@@ -4669,10 +4669,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>2.161</v>
+        <v>2.164</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>2.161</v>
+        <v>2.164</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>0</v>
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="B5" s="17" t="n">
-        <v>-0.39</v>
+        <v>-0.427</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>2.284</v>
+        <v>2.415</v>
       </c>
       <c r="D5" s="17" t="n">
         <v>0</v>
@@ -4697,13 +4697,13 @@
         <v>1</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>1.601</v>
+        <v>1.609</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>1.664</v>
+        <v>1.68</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>0.063</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -4713,10 +4713,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1.409</v>
+        <v>1.413</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>36.625</v>
+        <v>36.421</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>0</v>
@@ -4725,10 +4725,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>4.599</v>
+        <v>4.604</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>4.599</v>
+        <v>4.604</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>0</v>
@@ -4793,16 +4793,16 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.729</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>8.85</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>9.470000000000001</v>
@@ -4811,13 +4811,13 @@
         <v>75.8</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>2.517</v>
+        <v>4.396</v>
       </c>
     </row>
     <row r="10">
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>1.267</v>
+        <v>1.244</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>0.829</v>
+        <v>0.8242</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>442</v>
+        <v>459</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>8.76</v>
@@ -4845,10 +4845,10 @@
         <v>76.5</v>
       </c>
       <c r="H10" s="17" t="n">
-        <v>5.91</v>
+        <v>5.75</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="J10" s="17" t="n">
         <v>0.305</v>
@@ -4861,13 +4861,13 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>0.442</v>
+        <v>0.45</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>0.6341</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>3388</v>
+        <v>3261</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>15.56</v>
@@ -4879,13 +4879,13 @@
         <v>79.2</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>5.404</v>
+        <v>9.714</v>
       </c>
     </row>
   </sheetData>
@@ -4969,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>370553.66</v>
+        <v>370409.41</v>
       </c>
     </row>
     <row r="6">
@@ -4998,13 +4998,13 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>1726390.64</v>
+        <v>3618935.84</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1864541.85</v>
+        <v>3949274.76</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1534315.52</v>
+        <v>3425320.55</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>653381.46</v>
@@ -5017,16 +5017,16 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>2551297.09</v>
+        <v>4443842.29</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>2699830.52</v>
+        <v>4784563.43</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2502811.9</v>
+        <v>4393816.93</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>1827963.86</v>
+        <v>1827819.61</v>
       </c>
     </row>
     <row r="9">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>735309.64</v>
+        <v>2627908.71</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>769208.33</v>
+        <v>2853783.3</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>563958.29</v>
+        <v>2455077.39</v>
       </c>
       <c r="E10" s="15" t="n">
         <v>0</v>
@@ -5074,13 +5074,13 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>1544041.45</v>
+        <v>3436640.52</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1588118.79</v>
+        <v>3672693.76</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1513464.55</v>
+        <v>3404583.65</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>788263.47</v>
@@ -5093,16 +5093,16 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1007255.64</v>
+        <v>1007201.77</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>1111711.73</v>
+        <v>1111869.67</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>989347.35</v>
+        <v>989233.28</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>1039700.39</v>
+        <v>1039556.14</v>
       </c>
     </row>
     <row r="13">
@@ -5112,13 +5112,13 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>2.517</v>
+        <v>4.396</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>2.414</v>
+        <v>4.288</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2.511</v>
+        <v>4.422</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>1.387</v>
@@ -5131,13 +5131,13 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>0.911</v>
+        <v>2.79</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>0.9409999999999999</v>
+        <v>2.815</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>0.591</v>
+        <v>2.503</v>
       </c>
       <c r="E14" s="17" t="n">
         <v>-0.13</v>
@@ -5150,13 +5150,13 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>507024.49</v>
+        <v>885533.53</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>536690.46</v>
+        <v>953637.04</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>496764.36</v>
+        <v>874965.36</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>288328.99</v>
@@ -5169,16 +5169,16 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>500231.15</v>
+        <v>121668.24</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>575021.27</v>
+        <v>158232.63</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>492582.99</v>
+        <v>114267.92</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>751371.4</v>
+        <v>751227.15</v>
       </c>
     </row>
     <row r="17">
@@ -5188,13 +5188,13 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="7" t="n">
         <v>-0</v>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>0</v>
@@ -5241,13 +5241,13 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>1007255.64</v>
+        <v>1007201.77</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1111711.73</v>
+        <v>1111869.67</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>989347.35</v>
+        <v>989233.28</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>653381.46</v>
@@ -5279,13 +5279,13 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>1726390.64</v>
+        <v>3618935.84</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1864541.85</v>
+        <v>3949274.76</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1534315.52</v>
+        <v>3425320.55</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>653381.46</v>
@@ -5298,13 +5298,13 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>719135</v>
+        <v>2611734.07</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>752830.12</v>
+        <v>2837405.09</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>544968.17</v>
+        <v>2436087.27</v>
       </c>
       <c r="E24" s="15" t="n">
         <v>0</v>
@@ -5317,13 +5317,13 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>1007255.64</v>
+        <v>1007201.77</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1111711.73</v>
+        <v>1111869.67</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>989347.35</v>
+        <v>989233.28</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>653381.46</v>
@@ -5459,7 +5459,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>370553.66</v>
+        <v>370409.41</v>
       </c>
     </row>
     <row r="33">
@@ -5469,16 +5469,16 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>1007255.64</v>
+        <v>1007201.77</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1111711.73</v>
+        <v>1111869.67</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>989347.35</v>
+        <v>989233.28</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1039700.39</v>
+        <v>1039556.14</v>
       </c>
     </row>
     <row r="34">
@@ -5541,16 +5541,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>482954.15</v>
+        <v>481922.81</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>478172.49</v>
+        <v>477131.37</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>420313.98</v>
+        <v>419273.64</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>520326.12</v>
+        <v>519221.94</v>
       </c>
     </row>
     <row r="40">
@@ -5598,16 +5598,16 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>658473.52</v>
+        <v>657442.1800000001</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>659717.39</v>
+        <v>658676.27</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>723536.11</v>
+        <v>722495.77</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>701735.27</v>
+        <v>700631.09</v>
       </c>
     </row>
     <row r="43">
@@ -5674,16 +5674,16 @@
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>570328.12</v>
+        <v>569296.78</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>575736.35</v>
+        <v>574695.23</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>575306.51</v>
+        <v>574266.17</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>610611.27</v>
+        <v>609507.09</v>
       </c>
     </row>
     <row r="47">
@@ -5696,13 +5696,13 @@
         <v>0.305</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>0.312</v>
+        <v>0.313</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0.522</v>
+        <v>0.523</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>0.294</v>
+        <v>0.295</v>
       </c>
     </row>
     <row r="48">
@@ -5750,16 +5750,16 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>535576.83</v>
+        <v>534545.49</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>539763.29</v>
+        <v>538722.17</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>515255</v>
+        <v>514214.66</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>574693.9399999999</v>
+        <v>573589.76</v>
       </c>
     </row>
     <row r="51">
@@ -5775,7 +5775,7 @@
         <v>0</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E51" s="7" t="n">
         <v>0</v>
@@ -6031,16 +6031,16 @@
         </is>
       </c>
       <c r="B66" s="13" t="n">
-        <v>482954.15</v>
+        <v>481922.81</v>
       </c>
       <c r="C66" s="13" t="n">
-        <v>478172.49</v>
+        <v>477131.37</v>
       </c>
       <c r="D66" s="13" t="n">
-        <v>420313.98</v>
+        <v>419273.64</v>
       </c>
       <c r="E66" s="13" t="n">
-        <v>520326.12</v>
+        <v>519221.94</v>
       </c>
     </row>
     <row r="67">
@@ -6050,16 +6050,16 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
-        <v>570328.12</v>
+        <v>569296.78</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>575736.35</v>
+        <v>574695.23</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>575306.51</v>
+        <v>574266.17</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>610611.27</v>
+        <v>609507.09</v>
       </c>
     </row>
     <row r="68">
@@ -6160,13 +6160,13 @@
         </is>
       </c>
       <c r="B75" s="4" t="n">
-        <v>1640779.58</v>
+        <v>3533324.78</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>1768657.61</v>
+        <v>3853390.52</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>1382287.58</v>
+        <v>3273292.61</v>
       </c>
       <c r="E75" s="4" t="n">
         <v>564918.79</v>
@@ -6179,13 +6179,13 @@
         </is>
       </c>
       <c r="B76" s="13" t="n">
-        <v>2375777.72</v>
+        <v>4268322.92</v>
       </c>
       <c r="C76" s="13" t="n">
-        <v>2518285.62</v>
+        <v>4603018.53</v>
       </c>
       <c r="D76" s="13" t="n">
-        <v>2199589.77</v>
+        <v>4090594.8</v>
       </c>
       <c r="E76" s="13" t="n">
         <v>1276001.05</v>
@@ -6217,16 +6217,16 @@
         </is>
       </c>
       <c r="B78" s="13" t="n">
-        <v>1218263.78</v>
+        <v>3109831.52</v>
       </c>
       <c r="C78" s="13" t="n">
-        <v>1247380.81</v>
+        <v>3330914.67</v>
       </c>
       <c r="D78" s="13" t="n">
-        <v>984272.27</v>
+        <v>2874351.03</v>
       </c>
       <c r="E78" s="13" t="n">
-        <v>149772.46</v>
+        <v>148812.53</v>
       </c>
     </row>
     <row r="79">
@@ -6236,16 +6236,16 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>1938850.19</v>
+        <v>3830417.93</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>1982310.23</v>
+        <v>4065844.09</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>1785548.93</v>
+        <v>3675627.69</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>846911.9300000001</v>
+        <v>845952</v>
       </c>
     </row>
     <row r="80">
@@ -6255,16 +6255,16 @@
         </is>
       </c>
       <c r="B80" s="13" t="n">
-        <v>436927.53</v>
+        <v>437904.99</v>
       </c>
       <c r="C80" s="13" t="n">
-        <v>535975.39</v>
+        <v>537174.4399999999</v>
       </c>
       <c r="D80" s="13" t="n">
-        <v>414040.84</v>
+        <v>414967.11</v>
       </c>
       <c r="E80" s="13" t="n">
-        <v>429089.12</v>
+        <v>430049.05</v>
       </c>
     </row>
     <row r="81">
@@ -6274,16 +6274,16 @@
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>5.404</v>
+        <v>9.714</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>4.671</v>
+        <v>8.542</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>5.274</v>
+        <v>9.819000000000001</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>2.941</v>
+        <v>2.935</v>
       </c>
     </row>
     <row r="82">
@@ -6293,16 +6293,16 @@
         </is>
       </c>
       <c r="B82" s="17" t="n">
-        <v>2.106</v>
+        <v>6.423</v>
       </c>
       <c r="C82" s="17" t="n">
-        <v>1.929</v>
+        <v>5.805</v>
       </c>
       <c r="D82" s="17" t="n">
-        <v>1.403</v>
+        <v>5.957</v>
       </c>
       <c r="E82" s="17" t="n">
-        <v>-0.308</v>
+        <v>-0.307</v>
       </c>
     </row>
     <row r="83">
@@ -6312,13 +6312,13 @@
         </is>
       </c>
       <c r="B83" s="4" t="n">
-        <v>472273.2</v>
+        <v>850782.24</v>
       </c>
       <c r="C83" s="4" t="n">
-        <v>500717.41</v>
+        <v>917663.99</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>436712.85</v>
+        <v>814913.85</v>
       </c>
       <c r="E83" s="4" t="n">
         <v>252411.65</v>
@@ -6331,16 +6331,16 @@
         </is>
       </c>
       <c r="B84" s="18" t="n">
-        <v>-35345.67</v>
-      </c>
-      <c r="C84" s="13" t="n">
-        <v>35257.98</v>
+        <v>-412877.25</v>
+      </c>
+      <c r="C84" s="18" t="n">
+        <v>-380489.55</v>
       </c>
       <c r="D84" s="18" t="n">
-        <v>-22672.01</v>
+        <v>-399946.74</v>
       </c>
       <c r="E84" s="13" t="n">
-        <v>176677.47</v>
+        <v>177637.4</v>
       </c>
     </row>
     <row r="85">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="B85" s="7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E85" s="7" t="n">
         <v>0</v>
@@ -6403,16 +6403,16 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
-        <v>436927.53</v>
+        <v>437904.99</v>
       </c>
       <c r="C89" s="4" t="n">
-        <v>535975.39</v>
+        <v>537174.4399999999</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>414040.84</v>
+        <v>414967.11</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>429089.12</v>
+        <v>430049.05</v>
       </c>
     </row>
     <row r="90">
@@ -6441,13 +6441,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>1640779.58</v>
+        <v>3533324.78</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>1768657.61</v>
+        <v>3853390.52</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>1382287.58</v>
+        <v>3273292.61</v>
       </c>
       <c r="E91" s="4" t="n">
         <v>564918.79</v>
@@ -6460,16 +6460,16 @@
         </is>
       </c>
       <c r="B92" s="13" t="n">
-        <v>1203852.05</v>
+        <v>3095419.79</v>
       </c>
       <c r="C92" s="13" t="n">
-        <v>1232682.22</v>
+        <v>3316216.08</v>
       </c>
       <c r="D92" s="13" t="n">
-        <v>968246.74</v>
+        <v>2858325.5</v>
       </c>
       <c r="E92" s="13" t="n">
-        <v>135829.67</v>
+        <v>134869.74</v>
       </c>
     </row>
     <row r="93">
@@ -6479,16 +6479,16 @@
         </is>
       </c>
       <c r="B93" s="4" t="n">
-        <v>436927.53</v>
+        <v>437904.99</v>
       </c>
       <c r="C93" s="4" t="n">
-        <v>535975.39</v>
+        <v>537174.4399999999</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>414040.84</v>
+        <v>414967.11</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>429089.12</v>
+        <v>430049.05</v>
       </c>
     </row>
     <row r="94">
@@ -6615,10 +6615,10 @@
         <v>0</v>
       </c>
       <c r="C100" s="15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D100" s="15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E100" s="15" t="n">
         <v>0</v>
@@ -6631,16 +6631,16 @@
         </is>
       </c>
       <c r="B101" s="4" t="n">
-        <v>436927.53</v>
+        <v>437904.99</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>535975.39</v>
+        <v>537174.4399999999</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>414040.84</v>
+        <v>414967.11</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>429089.12</v>
+        <v>430049.05</v>
       </c>
     </row>
     <row r="102">
@@ -6734,16 +6734,16 @@
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>-104456.09</v>
+        <v>-104667.9</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>17908.29</v>
+        <v>17968.49</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>-32444.75</v>
+        <v>-32354.37</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>85756.85000000001</v>
+        <v>85702.98</v>
       </c>
     </row>
     <row r="6">
@@ -6753,16 +6753,16 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>100.73</v>
+        <v>359.99</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>503.64</v>
+        <v>1799.94</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>2115.27</v>
+        <v>7559.74</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>15008.37</v>
+        <v>53638.14</v>
       </c>
     </row>
     <row r="7">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>13308.99</v>
+        <v>1905854.19</v>
       </c>
     </row>
     <row r="9">
@@ -6816,16 +6816,16 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>-5408.23</v>
+        <v>-5398.45</v>
       </c>
       <c r="C11" s="19" t="n">
-        <v>-4978.39</v>
+        <v>-4969.39</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>-40283.15</v>
+        <v>-40210.31</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>60996.18</v>
+        <v>59964.84</v>
       </c>
     </row>
     <row r="12">
@@ -6898,16 +6898,16 @@
         </is>
       </c>
       <c r="B17" s="19" t="n">
-        <v>-99047.86</v>
+        <v>-99269.45</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>22886.69</v>
+        <v>22937.88</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>7838.41</v>
+        <v>7855.94</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>24760.68</v>
+        <v>25738.14</v>
       </c>
     </row>
     <row r="18">
@@ -6917,16 +6917,16 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>166.89</v>
+        <v>426</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>834.4299999999999</v>
+        <v>2130.02</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>3504.59</v>
+        <v>8946.09</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>24865.93</v>
+        <v>63474.64</v>
       </c>
     </row>
     <row r="19">
@@ -6936,7 +6936,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>14788.67</v>
+        <v>1907333.87</v>
       </c>
     </row>
     <row r="21">
@@ -7018,13 +7018,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1111711.73</v>
+        <v>1111869.67</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>989347.35</v>
+        <v>989233.28</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1039700.39</v>
+        <v>1039556.14</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>921498.79</v>
@@ -7037,16 +7037,16 @@
         </is>
       </c>
       <c r="B6" s="18" t="n">
-        <v>-104456.09</v>
+        <v>-104667.9</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>17908.29</v>
+        <v>17968.49</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>-32444.75</v>
+        <v>-32354.37</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>85756.85000000001</v>
+        <v>85702.98</v>
       </c>
     </row>
     <row r="7">
@@ -7094,16 +7094,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1007255.64</v>
+        <v>1007201.77</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1007255.64</v>
+        <v>1007201.77</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1007255.64</v>
+        <v>1007201.77</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1007255.64</v>
+        <v>1007201.77</v>
       </c>
     </row>
     <row r="10">
@@ -7113,16 +7113,16 @@
         </is>
       </c>
       <c r="B10" s="20" t="n">
-        <v>-9.4</v>
+        <v>-9.41</v>
       </c>
       <c r="C10" s="21" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="D10" s="20" t="n">
-        <v>-3.12</v>
+        <v>-3.11</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>9.31</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -7132,13 +7132,13 @@
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>-9.4</v>
+        <v>-9.41</v>
       </c>
       <c r="C11" s="22" t="n">
-        <v>-9.4</v>
+        <v>-9.41</v>
       </c>
       <c r="D11" s="22" t="n">
-        <v>-9.4</v>
+        <v>-9.41</v>
       </c>
       <c r="E11" s="22" t="n">
         <v>-9.470000000000001</v>
@@ -7185,13 +7185,13 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>575736.35</v>
+        <v>574695.23</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>575306.51</v>
+        <v>574266.17</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>610611.27</v>
+        <v>609507.09</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>509331.94</v>
@@ -7204,16 +7204,16 @@
         </is>
       </c>
       <c r="B16" s="18" t="n">
-        <v>-5408.23</v>
+        <v>-5398.45</v>
       </c>
       <c r="C16" s="18" t="n">
-        <v>-4978.39</v>
+        <v>-4969.39</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>-40283.15</v>
+        <v>-40210.31</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>60996.18</v>
+        <v>59964.84</v>
       </c>
     </row>
     <row r="17">
@@ -7261,16 +7261,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>570328.12</v>
+        <v>569296.78</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>570328.12</v>
+        <v>569296.78</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>570328.12</v>
+        <v>569296.78</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>570328.12</v>
+        <v>569296.78</v>
       </c>
     </row>
     <row r="20">
@@ -7289,7 +7289,7 @@
         <v>-6.6</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>11.98</v>
+        <v>11.77</v>
       </c>
     </row>
     <row r="21">
@@ -7352,13 +7352,13 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>535975.39</v>
+        <v>537174.4399999999</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>414040.84</v>
+        <v>414967.11</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>429089.12</v>
+        <v>430049.05</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>412166.85</v>
@@ -7371,16 +7371,16 @@
         </is>
       </c>
       <c r="B26" s="18" t="n">
-        <v>-99047.86</v>
+        <v>-99269.45</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>22886.69</v>
+        <v>22937.88</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>7838.41</v>
+        <v>7855.94</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>24760.68</v>
+        <v>25738.14</v>
       </c>
     </row>
     <row r="27">
@@ -7428,16 +7428,16 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>436927.53</v>
+        <v>437904.99</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>436927.53</v>
+        <v>437904.99</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>436927.53</v>
+        <v>437904.99</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>436927.53</v>
+        <v>437904.99</v>
       </c>
     </row>
     <row r="30">
@@ -7456,7 +7456,7 @@
         <v>1.83</v>
       </c>
       <c r="E30" s="21" t="n">
-        <v>6.01</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="31">
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>17908.29</v>
+        <v>17968.49</v>
       </c>
     </row>
     <row r="5">
@@ -7535,7 +7535,7 @@
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>-332849.58</v>
+        <v>-334389.75</v>
       </c>
     </row>
     <row r="6">
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>171351.35</v>
+        <v>172831.32</v>
       </c>
     </row>
     <row r="7">
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="B96" s="4" t="n">
-        <v>1011218.51</v>
+        <v>1011202.12</v>
       </c>
     </row>
     <row r="97">
@@ -8562,7 +8562,7 @@
         </is>
       </c>
       <c r="B97" s="13" t="n">
-        <v>1025407</v>
+        <v>1025356.19</v>
       </c>
     </row>
     <row r="98">
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="B98" s="4" t="n">
-        <v>1026941.31</v>
+        <v>1026905.51</v>
       </c>
     </row>
     <row r="99">
@@ -8582,7 +8582,7 @@
         </is>
       </c>
       <c r="B99" s="13" t="n">
-        <v>1015258.85</v>
+        <v>1015273.3</v>
       </c>
     </row>
     <row r="100">
@@ -8592,7 +8592,7 @@
         </is>
       </c>
       <c r="B100" s="4" t="n">
-        <v>1003003.03</v>
+        <v>1003025.8</v>
       </c>
     </row>
     <row r="101">
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="B101" s="13" t="n">
-        <v>1013068.4</v>
+        <v>1013098.34</v>
       </c>
     </row>
     <row r="102">
@@ -8612,7 +8612,7 @@
         </is>
       </c>
       <c r="B102" s="4" t="n">
-        <v>1026667.89</v>
+        <v>1026718.34</v>
       </c>
     </row>
     <row r="103">
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="B103" s="13" t="n">
-        <v>1053397.75</v>
+        <v>1053504.94</v>
       </c>
     </row>
     <row r="104">
@@ -8632,7 +8632,7 @@
         </is>
       </c>
       <c r="B104" s="4" t="n">
-        <v>1050736.08</v>
+        <v>1050844.96</v>
       </c>
     </row>
     <row r="105">
@@ -8642,7 +8642,7 @@
         </is>
       </c>
       <c r="B105" s="13" t="n">
-        <v>1049499.07</v>
+        <v>1049581.91</v>
       </c>
     </row>
     <row r="106">
@@ -8652,7 +8652,7 @@
         </is>
       </c>
       <c r="B106" s="4" t="n">
-        <v>1049134.93</v>
+        <v>1049200.21</v>
       </c>
     </row>
     <row r="107">
@@ -8662,7 +8662,7 @@
         </is>
       </c>
       <c r="B107" s="13" t="n">
-        <v>1042919.9</v>
+        <v>1042965.78</v>
       </c>
     </row>
     <row r="108">
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="B108" s="4" t="n">
-        <v>1048685.92</v>
+        <v>1048734.43</v>
       </c>
     </row>
     <row r="109">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="B109" s="13" t="n">
-        <v>1042773.4</v>
+        <v>1042822.5</v>
       </c>
     </row>
     <row r="110">
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="B110" s="4" t="n">
-        <v>1044235.83</v>
+        <v>1044292.9</v>
       </c>
     </row>
     <row r="111">
@@ -8702,7 +8702,7 @@
         </is>
       </c>
       <c r="B111" s="13" t="n">
-        <v>1070354.14</v>
+        <v>1070408.83</v>
       </c>
     </row>
     <row r="112">
@@ -8712,7 +8712,7 @@
         </is>
       </c>
       <c r="B112" s="4" t="n">
-        <v>1061514.84</v>
+        <v>1061559.43</v>
       </c>
     </row>
     <row r="113">
@@ -8722,7 +8722,7 @@
         </is>
       </c>
       <c r="B113" s="13" t="n">
-        <v>1074870.62</v>
+        <v>1074879.59</v>
       </c>
     </row>
     <row r="114">
@@ -8732,7 +8732,7 @@
         </is>
       </c>
       <c r="B114" s="4" t="n">
-        <v>1080512.52</v>
+        <v>1080503.54</v>
       </c>
     </row>
     <row r="115">
@@ -8742,7 +8742,7 @@
         </is>
       </c>
       <c r="B115" s="13" t="n">
-        <v>1086924.48</v>
+        <v>1086894.67</v>
       </c>
     </row>
     <row r="116">
@@ -8752,7 +8752,7 @@
         </is>
       </c>
       <c r="B116" s="4" t="n">
-        <v>1071780.32</v>
+        <v>1071796.37</v>
       </c>
     </row>
     <row r="117">
@@ -8762,7 +8762,7 @@
         </is>
       </c>
       <c r="B117" s="13" t="n">
-        <v>1065526.09</v>
+        <v>1065522.69</v>
       </c>
     </row>
     <row r="118">
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="B118" s="4" t="n">
-        <v>1080594.32</v>
+        <v>1080563.67</v>
       </c>
     </row>
     <row r="119">
@@ -8782,7 +8782,7 @@
         </is>
       </c>
       <c r="B119" s="13" t="n">
-        <v>1075591.99</v>
+        <v>1075540.76</v>
       </c>
     </row>
     <row r="120">
@@ -8792,7 +8792,7 @@
         </is>
       </c>
       <c r="B120" s="4" t="n">
-        <v>1071013.67</v>
+        <v>1070952.2</v>
       </c>
     </row>
     <row r="121">
@@ -8802,7 +8802,7 @@
         </is>
       </c>
       <c r="B121" s="13" t="n">
-        <v>1073689.47</v>
+        <v>1073612.17</v>
       </c>
     </row>
     <row r="122">
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="B122" s="4" t="n">
-        <v>1074236.64</v>
+        <v>1074160.56</v>
       </c>
     </row>
     <row r="123">
@@ -8822,7 +8822,7 @@
         </is>
       </c>
       <c r="B123" s="13" t="n">
-        <v>1084547.15</v>
+        <v>1084460.75</v>
       </c>
     </row>
     <row r="124">
@@ -8832,7 +8832,7 @@
         </is>
       </c>
       <c r="B124" s="4" t="n">
-        <v>1085528.37</v>
+        <v>1085444.17</v>
       </c>
     </row>
     <row r="125">
@@ -8842,7 +8842,7 @@
         </is>
       </c>
       <c r="B125" s="13" t="n">
-        <v>1092616.33</v>
+        <v>1092531.84</v>
       </c>
     </row>
     <row r="126">
@@ -8852,7 +8852,7 @@
         </is>
       </c>
       <c r="B126" s="4" t="n">
-        <v>1092781.06</v>
+        <v>1092690.79</v>
       </c>
     </row>
     <row r="127">
@@ -8862,7 +8862,7 @@
         </is>
       </c>
       <c r="B127" s="13" t="n">
-        <v>1053336.82</v>
+        <v>1053158.31</v>
       </c>
     </row>
     <row r="128">
@@ -8872,7 +8872,7 @@
         </is>
       </c>
       <c r="B128" s="4" t="n">
-        <v>1049687.33</v>
+        <v>1049512.64</v>
       </c>
     </row>
     <row r="129">
@@ -8882,7 +8882,7 @@
         </is>
       </c>
       <c r="B129" s="13" t="n">
-        <v>1044100.12</v>
+        <v>1043936.06</v>
       </c>
     </row>
     <row r="130">
@@ -8892,7 +8892,7 @@
         </is>
       </c>
       <c r="B130" s="4" t="n">
-        <v>1032626.83</v>
+        <v>1032472.74</v>
       </c>
     </row>
     <row r="131">
@@ -8902,7 +8902,7 @@
         </is>
       </c>
       <c r="B131" s="13" t="n">
-        <v>1039700.39</v>
+        <v>1039556.14</v>
       </c>
     </row>
     <row r="132">
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="B132" s="4" t="n">
-        <v>1037551.62</v>
+        <v>1037415.03</v>
       </c>
     </row>
     <row r="133">
@@ -8922,7 +8922,7 @@
         </is>
       </c>
       <c r="B133" s="13" t="n">
-        <v>1019311.74</v>
+        <v>1019194.66</v>
       </c>
     </row>
     <row r="134">
@@ -8932,7 +8932,7 @@
         </is>
       </c>
       <c r="B134" s="4" t="n">
-        <v>1014163.76</v>
+        <v>1014068.88</v>
       </c>
     </row>
     <row r="135">
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="B135" s="13" t="n">
-        <v>999293.04</v>
+        <v>999221.6800000001</v>
       </c>
     </row>
     <row r="136">
@@ -8952,7 +8952,7 @@
         </is>
       </c>
       <c r="B136" s="4" t="n">
-        <v>1011409.78</v>
+        <v>1011311.18</v>
       </c>
     </row>
     <row r="137">
@@ -8962,7 +8962,7 @@
         </is>
       </c>
       <c r="B137" s="13" t="n">
-        <v>1014540.8</v>
+        <v>1014433.88</v>
       </c>
     </row>
     <row r="138">
@@ -8972,7 +8972,7 @@
         </is>
       </c>
       <c r="B138" s="4" t="n">
-        <v>1011881.11</v>
+        <v>1011774.92</v>
       </c>
     </row>
     <row r="139">
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="B139" s="13" t="n">
-        <v>998415.39</v>
+        <v>998320.26</v>
       </c>
     </row>
     <row r="140">
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B140" s="4" t="n">
-        <v>1014351.76</v>
+        <v>1014291.81</v>
       </c>
     </row>
     <row r="141">
@@ -9002,7 +9002,7 @@
         </is>
       </c>
       <c r="B141" s="13" t="n">
-        <v>1023498.77</v>
+        <v>1023430.49</v>
       </c>
     </row>
     <row r="142">
@@ -9012,7 +9012,7 @@
         </is>
       </c>
       <c r="B142" s="4" t="n">
-        <v>1023696.66</v>
+        <v>1023647.26</v>
       </c>
     </row>
     <row r="143">
@@ -9022,7 +9022,7 @@
         </is>
       </c>
       <c r="B143" s="13" t="n">
-        <v>996887.45</v>
+        <v>996791.04</v>
       </c>
     </row>
     <row r="144">
@@ -9032,7 +9032,7 @@
         </is>
       </c>
       <c r="B144" s="4" t="n">
-        <v>1016573.57</v>
+        <v>1016545.25</v>
       </c>
     </row>
     <row r="145">
@@ -9042,7 +9042,7 @@
         </is>
       </c>
       <c r="B145" s="13" t="n">
-        <v>997861.24</v>
+        <v>997800.67</v>
       </c>
     </row>
     <row r="146">
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="B146" s="4" t="n">
-        <v>991493.7</v>
+        <v>991400.37</v>
       </c>
     </row>
     <row r="147">
@@ -9062,7 +9062,7 @@
         </is>
       </c>
       <c r="B147" s="13" t="n">
-        <v>989347.35</v>
+        <v>989233.28</v>
       </c>
     </row>
     <row r="148">
@@ -9072,7 +9072,7 @@
         </is>
       </c>
       <c r="B148" s="4" t="n">
-        <v>1004898.62</v>
+        <v>1004807.41</v>
       </c>
     </row>
     <row r="149">
@@ -9082,7 +9082,7 @@
         </is>
       </c>
       <c r="B149" s="13" t="n">
-        <v>1099657.36</v>
+        <v>1099781.06</v>
       </c>
     </row>
     <row r="150">
@@ -9092,7 +9092,7 @@
         </is>
       </c>
       <c r="B150" s="4" t="n">
-        <v>1108417.28</v>
+        <v>1108558.05</v>
       </c>
     </row>
     <row r="151">
@@ -9102,7 +9102,7 @@
         </is>
       </c>
       <c r="B151" s="13" t="n">
-        <v>1111711.73</v>
+        <v>1111869.67</v>
       </c>
     </row>
     <row r="152">
@@ -9112,7 +9112,7 @@
         </is>
       </c>
       <c r="B152" s="4" t="n">
-        <v>1007255.64</v>
+        <v>1007201.77</v>
       </c>
     </row>
   </sheetData>
@@ -9217,31 +9217,31 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1007255.64</v>
+        <v>1007201.77</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1726390.64</v>
+        <v>3618935.84</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>808731.8100000001</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2535122.45</v>
+        <v>4427667.65</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>917658.83</v>
+        <v>2810204.03</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>2.517</v>
+        <v>4.396</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.911</v>
+        <v>2.79</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>251.69</v>
+        <v>439.6</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>125.84</v>
+        <v>219.8</v>
       </c>
       <c r="K4" s="23" t="n">
         <v>14</v>
@@ -9254,7 +9254,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>570328.12</v>
+        <v>569296.78</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>85611.06</v>
@@ -9275,10 +9275,10 @@
         <v>-0.004</v>
       </c>
       <c r="I5" s="24" t="n">
-        <v>30.47</v>
+        <v>30.52</v>
       </c>
       <c r="J5" s="24" t="n">
-        <v>15.23</v>
+        <v>15.26</v>
       </c>
       <c r="K5" s="25" t="n">
         <v>1</v>
@@ -9291,31 +9291,31 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>436927.53</v>
+        <v>437904.99</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1640779.58</v>
+        <v>3533324.78</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>720586.41</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2361365.99</v>
+        <v>4253911.19</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>920193.17</v>
+        <v>2812738.37</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>5.404</v>
+        <v>9.714</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>2.106</v>
+        <v>6.423</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>540.45</v>
+        <v>971.42</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>270.22</v>
+        <v>485.71</v>
       </c>
       <c r="K6" s="23" t="n">
         <v>13</v>
@@ -9356,7 +9356,7 @@
     <row r="3">
       <c r="A3" s="26" t="inlineStr">
         <is>
-          <t>HHI=0.075  ·  effective N pairs=13.3  ·  max pair=10.02% of gross</t>
+          <t>HHI=0.1498  ·  effective N pairs=6.7  ·  max pair=29.52% of gross</t>
         </is>
       </c>
     </row>
@@ -9395,20 +9395,20 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>342668.34</v>
+        <v>2102828</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>342668.34</v>
+        <v>2102828</v>
       </c>
       <c r="D6" s="27" t="n">
-        <v>34.02</v>
+        <v>208.78</v>
       </c>
       <c r="E6" s="27" t="n">
-        <v>13.52</v>
+        <v>47.49</v>
       </c>
       <c r="F6" s="23" t="n">
         <v>2</v>
@@ -9417,20 +9417,20 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>269574</v>
+        <v>342668.34</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>269574</v>
+        <v>342668.34</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>26.76</v>
+        <v>34.02</v>
       </c>
       <c r="E7" s="21" t="n">
-        <v>10.63</v>
+        <v>7.74</v>
       </c>
       <c r="F7" s="25" t="n">
         <v>2</v>
@@ -9439,20 +9439,20 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>261427.36</v>
+        <v>269574</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>261427.36</v>
+        <v>269574</v>
       </c>
       <c r="D8" s="27" t="n">
-        <v>25.95</v>
+        <v>26.76</v>
       </c>
       <c r="E8" s="27" t="n">
-        <v>10.31</v>
+        <v>6.09</v>
       </c>
       <c r="F8" s="23" t="n">
         <v>2</v>
@@ -9461,20 +9461,20 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>221871.36</v>
+        <v>261427.36</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>221871.36</v>
+        <v>261427.36</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>22.03</v>
+        <v>25.96</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>8.75</v>
+        <v>5.9</v>
       </c>
       <c r="F9" s="25" t="n">
         <v>2</v>
@@ -9483,20 +9483,20 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>210282.8</v>
+        <v>221871.36</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>210282.8</v>
+        <v>221871.36</v>
       </c>
       <c r="D10" s="27" t="n">
-        <v>20.88</v>
+        <v>22.03</v>
       </c>
       <c r="E10" s="27" t="n">
-        <v>8.289999999999999</v>
+        <v>5.01</v>
       </c>
       <c r="F10" s="23" t="n">
         <v>2</v>
@@ -9518,7 +9518,7 @@
         <v>16.64</v>
       </c>
       <c r="E11" s="21" t="n">
-        <v>6.61</v>
+        <v>3.78</v>
       </c>
       <c r="F11" s="25" t="n">
         <v>1</v>
@@ -9540,7 +9540,7 @@
         <v>16.62</v>
       </c>
       <c r="E12" s="27" t="n">
-        <v>6.6</v>
+        <v>3.78</v>
       </c>
       <c r="F12" s="23" t="n">
         <v>2</v>
@@ -9562,7 +9562,7 @@
         <v>13.89</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>5.52</v>
+        <v>3.16</v>
       </c>
       <c r="F13" s="25" t="n">
         <v>2</v>
@@ -9584,7 +9584,7 @@
         <v>8.75</v>
       </c>
       <c r="E14" s="27" t="n">
-        <v>3.48</v>
+        <v>1.99</v>
       </c>
       <c r="F14" s="23" t="n">
         <v>1</v>
@@ -9606,7 +9606,7 @@
         <v>8.5</v>
       </c>
       <c r="E15" s="21" t="n">
-        <v>3.38</v>
+        <v>1.93</v>
       </c>
       <c r="F15" s="25" t="n">
         <v>1</v>
@@ -9653,16 +9653,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>861148.62</v>
+        <v>2753693.82</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>73678.78</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>787469.84</v>
+        <v>2680015.04</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>31.06</v>
+        <v>60.53</v>
       </c>
     </row>
     <row r="21">
@@ -9681,7 +9681,7 @@
         <v>-471861.66</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>-18.61</v>
+        <v>-10.66</v>
       </c>
     </row>
     <row r="22">
@@ -9700,7 +9700,7 @@
         <v>436962.62</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>17.24</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -9719,7 +9719,7 @@
         <v>290507.22</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>11.46</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="24">
@@ -9738,7 +9738,7 @@
         <v>-76705.2</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>-3.03</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="25">
@@ -9757,7 +9757,7 @@
         <v>-48713.99</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>-1.92</v>
+        <v>-1.1</v>
       </c>
     </row>
   </sheetData>
@@ -9795,7 +9795,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1.893</v>
+        <v>6.257</v>
       </c>
     </row>
     <row r="4">
@@ -9805,7 +9805,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>2.491</v>
+        <v>6.854</v>
       </c>
     </row>
     <row r="5">
@@ -9815,7 +9815,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>91.36</v>
+        <v>279.26</v>
       </c>
     </row>
     <row r="6">
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="B10" s="27" t="n">
-        <v>31.06</v>
+        <v>60.53</v>
       </c>
     </row>
     <row r="11">
@@ -9866,7 +9866,7 @@
         </is>
       </c>
       <c r="B11" s="20" t="n">
-        <v>-18.61</v>
+        <v>-10.66</v>
       </c>
     </row>
     <row r="12">
@@ -9876,7 +9876,7 @@
         </is>
       </c>
       <c r="B12" s="27" t="n">
-        <v>17.24</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -9886,7 +9886,7 @@
         </is>
       </c>
       <c r="B13" s="21" t="n">
-        <v>11.46</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="14">
@@ -9896,7 +9896,7 @@
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>-3.03</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="15">
@@ -9906,7 +9906,7 @@
         </is>
       </c>
       <c r="B15" s="20" t="n">
-        <v>-1.92</v>
+        <v>-1.1</v>
       </c>
     </row>
   </sheetData>

--- a/trading_signals/risk_management/risk_workbook_20260606_031417.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260606_031417.xlsx
@@ -728,7 +728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-05  ·  Generated 2026-06-24T18:50:34  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-05  ·  Generated 2026-06-25T01:17:51  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>

--- a/trading_signals/risk_management/risk_workbook_20260606_031417.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260606_031417.xlsx
@@ -728,7 +728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-05  ·  Generated 2026-06-25T01:17:51  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-05  ·  Generated 2026-06-25T01:35:43  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>

--- a/trading_signals/risk_management/risk_workbook_20260606_031417.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260606_031417.xlsx
@@ -728,7 +728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-05  ·  Generated 2026-06-25T01:35:43  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-05  ·  Generated 2026-06-25T01:49:07  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>4.396</v>
+        <v>2.517</v>
       </c>
     </row>
     <row r="6">
@@ -758,8 +758,8 @@
           <t>Net leverage (x)</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>2.79</v>
+      <c r="B6" s="6" t="n">
+        <v>0.911</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>6.257</v>
+        <v>1.893</v>
       </c>
     </row>
     <row r="8">
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>127447.75</v>
+        <v>41670.94</v>
       </c>
     </row>
     <row r="9">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>12.65</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="10">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>122.11</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="11">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>4.396</v>
+        <v>2.517</v>
       </c>
     </row>
     <row r="16">
@@ -862,7 +862,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>KLAC (208.78% NAV)</t>
+          <t>BWA (34.02% NAV)</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>60.53</v>
+        <v>31.06</v>
       </c>
     </row>
     <row r="18">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>127447.75</v>
+        <v>41670.94</v>
       </c>
     </row>
     <row r="4">
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>180208.79</v>
+        <v>58921.95</v>
       </c>
     </row>
     <row r="5">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1229890.77</v>
+        <v>402131.08</v>
       </c>
     </row>
     <row r="6">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>122.11</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="7">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>87294.89999999999</v>
+        <v>21335.46</v>
       </c>
     </row>
     <row r="8">
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>155333.59</v>
+        <v>47624.33</v>
       </c>
     </row>
     <row r="10">
@@ -1024,105 +1024,105 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>LRCX/BSX</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>61009.47</v>
+        <v>6378.93</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>47.87</v>
+        <v>15.31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>KLAC/LOW</t>
+          <t>LRCX/RMD</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>37861.22</v>
+        <v>5558.93</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>29.71</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>LRCX/BSX</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>6329.41</v>
+        <v>5083.22</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>4.97</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>LRCX/RMD</t>
+          <t>KLAC/LOW</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>5710.59</v>
+        <v>3082.96</v>
       </c>
       <c r="C15" s="17" t="n">
-        <v>4.48</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>BWA/CME</t>
+          <t>STLD/HII</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2451.12</v>
+        <v>2977.49</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>1.92</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>CSCO/CAG</t>
+          <t>STLD/ISRG</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>2119.47</v>
+        <v>2820.38</v>
       </c>
       <c r="C17" s="17" t="n">
-        <v>1.66</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>STLD/HII</t>
+          <t>CSCO/CAG</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>2086.97</v>
+        <v>2769.55</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>1.64</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>STLD/ISRG</t>
+          <t>BWA/CME</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>2086.05</v>
+        <v>2644.94</v>
       </c>
       <c r="C19" s="17" t="n">
-        <v>1.64</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="20">
@@ -1132,36 +1132,36 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>1760.83</v>
+        <v>2397.98</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>1.38</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>BWA/VLTO</t>
+          <t>CSCO/REGN</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1665.95</v>
+        <v>2213.83</v>
       </c>
       <c r="C21" s="17" t="n">
-        <v>1.31</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>BWA/VLTO</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>1562.69</v>
+        <v>2112.88</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>1.23</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="23">
@@ -1171,23 +1171,23 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1422.2</v>
+        <v>1767.25</v>
       </c>
       <c r="C23" s="17" t="n">
-        <v>1.12</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>CSCO/REGN</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>1331.04</v>
+        <v>1728.04</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>1.04</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="25">
@@ -1196,11 +1196,11 @@
           <t>HAS/PFE</t>
         </is>
       </c>
-      <c r="B25" s="15" t="n">
-        <v>50.74</v>
+      <c r="B25" s="13" t="n">
+        <v>134.56</v>
       </c>
       <c r="C25" s="17" t="n">
-        <v>0.04</v>
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -1325,7 +1325,7 @@
         <v>670</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1020220</v>
+        <v>10202197</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
@@ -1367,7 +1367,7 @@
         <v>420</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1020220</v>
+        <v>10202197</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0</v>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>-315103.07</v>
+        <v>-95331.64999999999</v>
       </c>
       <c r="C4" s="22" t="n">
-        <v>-31.29</v>
+        <v>-9.460000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>-630206.15</v>
+        <v>-190663.3</v>
       </c>
       <c r="C5" s="20" t="n">
-        <v>-62.57</v>
+        <v>-18.93</v>
       </c>
     </row>
     <row r="6">
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>-315103.07</v>
+        <v>-95331.64999999999</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>-31.29</v>
+        <v>-9.460000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="B7" s="18" t="n">
-        <v>-268001.5</v>
+        <v>-78746.98</v>
       </c>
       <c r="C7" s="20" t="n">
-        <v>-26.61</v>
+        <v>-7.82</v>
       </c>
     </row>
   </sheetData>
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>9.710000000000001</v>
+        <v>5.39</v>
       </c>
       <c r="D6" s="32" t="n">
         <v>3</v>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>6.42</v>
+        <v>2.1</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>0.5</v>
@@ -1857,11 +1857,11 @@
       </c>
       <c r="B8" s="32" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>208.78</v>
+        <v>34.02</v>
       </c>
       <c r="D8" s="32" t="n">
         <v>15</v>
@@ -1883,11 +1883,11 @@
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>34.02</v>
+        <v>26.76</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>15</v>
@@ -1909,11 +1909,11 @@
       </c>
       <c r="B10" s="32" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>26.76</v>
+        <v>25.96</v>
       </c>
       <c r="D10" s="32" t="n">
         <v>15</v>
@@ -1928,54 +1928,54 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>sector_net</t>
         </is>
       </c>
-      <c r="B11" s="32" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="C11" s="32" t="n">
-        <v>60.53</v>
-      </c>
-      <c r="D11" s="32" t="n">
+      <c r="C11" s="34" t="n">
+        <v>31.06</v>
+      </c>
+      <c r="D11" s="34" t="n">
         <v>30</v>
       </c>
-      <c r="E11" s="32" t="n">
+      <c r="E11" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="F11" s="32" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="F11" s="34" t="inlineStr">
+        <is>
+          <t>amber</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>max_pair</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>combined</t>
         </is>
       </c>
-      <c r="C12" s="34" t="n">
-        <v>29.52</v>
-      </c>
-      <c r="D12" s="34" t="n">
+      <c r="C12" s="30" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="D12" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="E12" s="34" t="n">
+      <c r="E12" s="30" t="n">
         <v>35</v>
       </c>
-      <c r="F12" s="34" t="inlineStr">
-        <is>
-          <t>amber</t>
+      <c r="F12" s="30" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>6.26</v>
+        <v>1.89</v>
       </c>
       <c r="D13" s="32" t="n">
         <v>0.3</v>
@@ -2006,28 +2006,28 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>var_95_1d</t>
         </is>
       </c>
-      <c r="B14" s="32" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>combined</t>
         </is>
       </c>
-      <c r="C14" s="32" t="n">
-        <v>12.65</v>
-      </c>
-      <c r="D14" s="32" t="n">
+      <c r="C14" s="34" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="D14" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="32" t="n">
+      <c r="E14" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="F14" s="32" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="F14" s="34" t="inlineStr">
+        <is>
+          <t>amber</t>
         </is>
       </c>
     </row>
@@ -2280,10 +2280,10 @@
         <v>670</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>1929.2</v>
+        <v>192.92</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>1292564</v>
+        <v>129256.4</v>
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
@@ -2368,10 +2368,10 @@
         <v>420</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>1929.2</v>
+        <v>192.92</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>810264</v>
+        <v>81026.39999999999</v>
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
@@ -3511,11 +3511,11 @@
           <t>KLAC/REGN</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>1157781.78</v>
+      <c r="C5" s="19" t="n">
+        <v>-5525.82</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1307179.35</v>
+        <v>143871.75</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>732046.3</v>
+        <v>2808.7</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>890766.6800000001</v>
+        <v>161529.08</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>1</v>
@@ -4187,81 +4187,81 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>LRCX/BSX</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>47.87</v>
+        <v>15.31</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>KLAC/LOW</t>
+          <t>LRCX/RMD</t>
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>29.71</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>LRCX/BSX</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>4.97</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>LRCX/RMD</t>
+          <t>KLAC/LOW</t>
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>4.48</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>BWA/CME</t>
+          <t>STLD/HII</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>1.92</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>CSCO/CAG</t>
+          <t>STLD/ISRG</t>
         </is>
       </c>
       <c r="B18" s="17" t="n">
-        <v>1.66</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>STLD/ISRG</t>
+          <t>CSCO/CAG</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>1.64</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>STLD/HII</t>
+          <t>BWA/CME</t>
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>1.64</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="21">
@@ -4271,27 +4271,27 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>1.38</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>BWA/VLTO</t>
+          <t>CSCO/REGN</t>
         </is>
       </c>
       <c r="B22" s="17" t="n">
-        <v>1.31</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>BWA/VLTO</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>1.23</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="24">
@@ -4301,17 +4301,17 @@
         </is>
       </c>
       <c r="B24" s="17" t="n">
-        <v>1.12</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>CSCO/REGN</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>1.04</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="26">
@@ -4321,7 +4321,7 @@
         </is>
       </c>
       <c r="B26" s="17" t="n">
-        <v>0.04</v>
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -4817,7 +4817,7 @@
         <v>1.34</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>4.396</v>
+        <v>2.517</v>
       </c>
     </row>
     <row r="10">
@@ -4885,7 +4885,7 @@
         <v>0.38</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>9.714</v>
+        <v>5.392</v>
       </c>
     </row>
   </sheetData>
@@ -4998,13 +4998,13 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>3618935.84</v>
+        <v>1726390.64</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3949274.76</v>
+        <v>1864541.85</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3425320.55</v>
+        <v>1534315.52</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>653381.46</v>
@@ -5017,13 +5017,13 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>4443842.29</v>
+        <v>2551297.09</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>4784563.43</v>
+        <v>2699830.52</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>4393816.93</v>
+        <v>2502811.9</v>
       </c>
       <c r="E8" s="13" t="n">
         <v>1827819.61</v>
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>2627908.71</v>
+        <v>735363.51</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>2853783.3</v>
+        <v>769050.39</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2455077.39</v>
+        <v>564072.36</v>
       </c>
       <c r="E10" s="15" t="n">
         <v>0</v>
@@ -5074,13 +5074,13 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>3436640.52</v>
+        <v>1544095.32</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3672693.76</v>
+        <v>1587960.85</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>3404583.65</v>
+        <v>1513578.62</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>788263.47</v>
@@ -5112,13 +5112,13 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>4.396</v>
+        <v>2.517</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>4.288</v>
+        <v>2.413</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>4.422</v>
+        <v>2.511</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>1.387</v>
@@ -5131,13 +5131,13 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>2.79</v>
+        <v>0.911</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>2.815</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>2.503</v>
+        <v>0.591</v>
       </c>
       <c r="E14" s="17" t="n">
         <v>-0.13</v>
@@ -5150,13 +5150,13 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>885533.53</v>
+        <v>507024.49</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>953637.04</v>
+        <v>536690.46</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>874965.36</v>
+        <v>496764.36</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>288328.99</v>
@@ -5169,13 +5169,13 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>121668.24</v>
+        <v>500177.28</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>158232.63</v>
+        <v>575179.21</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>114267.92</v>
+        <v>492468.92</v>
       </c>
       <c r="E16" s="13" t="n">
         <v>751227.15</v>
@@ -5191,10 +5191,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>0</v>
@@ -5279,13 +5279,13 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>3618935.84</v>
+        <v>1726390.64</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3949274.76</v>
+        <v>1864541.85</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3425320.55</v>
+        <v>1534315.52</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>653381.46</v>
@@ -5298,13 +5298,13 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>2611734.07</v>
+        <v>719188.87</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>2837405.09</v>
+        <v>752672.1800000001</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>2436087.27</v>
+        <v>545082.24</v>
       </c>
       <c r="E24" s="15" t="n">
         <v>0</v>
@@ -6160,13 +6160,13 @@
         </is>
       </c>
       <c r="B75" s="4" t="n">
-        <v>3533324.78</v>
+        <v>1640779.58</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>3853390.52</v>
+        <v>1768657.61</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>3273292.61</v>
+        <v>1382287.58</v>
       </c>
       <c r="E75" s="4" t="n">
         <v>564918.79</v>
@@ -6179,13 +6179,13 @@
         </is>
       </c>
       <c r="B76" s="13" t="n">
-        <v>4268322.92</v>
+        <v>2375777.72</v>
       </c>
       <c r="C76" s="13" t="n">
-        <v>4603018.53</v>
+        <v>2518285.62</v>
       </c>
       <c r="D76" s="13" t="n">
-        <v>4090594.8</v>
+        <v>2199589.77</v>
       </c>
       <c r="E76" s="13" t="n">
         <v>1276001.05</v>
@@ -6217,13 +6217,13 @@
         </is>
       </c>
       <c r="B78" s="13" t="n">
-        <v>3109831.52</v>
+        <v>1217286.32</v>
       </c>
       <c r="C78" s="13" t="n">
-        <v>3330914.67</v>
+        <v>1246181.76</v>
       </c>
       <c r="D78" s="13" t="n">
-        <v>2874351.03</v>
+        <v>983346</v>
       </c>
       <c r="E78" s="13" t="n">
         <v>148812.53</v>
@@ -6236,13 +6236,13 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>3830417.93</v>
+        <v>1937872.73</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>4065844.09</v>
+        <v>1981111.18</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>3675627.69</v>
+        <v>1784622.66</v>
       </c>
       <c r="E79" s="4" t="n">
         <v>845952</v>
@@ -6274,13 +6274,13 @@
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>9.714</v>
+        <v>5.392</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>8.542</v>
+        <v>4.661</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>9.819000000000001</v>
+        <v>5.262</v>
       </c>
       <c r="E81" s="7" t="n">
         <v>2.935</v>
@@ -6293,13 +6293,13 @@
         </is>
       </c>
       <c r="B82" s="17" t="n">
-        <v>6.423</v>
+        <v>2.101</v>
       </c>
       <c r="C82" s="17" t="n">
-        <v>5.805</v>
+        <v>1.924</v>
       </c>
       <c r="D82" s="17" t="n">
-        <v>5.957</v>
+        <v>1.4</v>
       </c>
       <c r="E82" s="17" t="n">
         <v>-0.307</v>
@@ -6312,13 +6312,13 @@
         </is>
       </c>
       <c r="B83" s="4" t="n">
-        <v>850782.24</v>
+        <v>472273.2</v>
       </c>
       <c r="C83" s="4" t="n">
-        <v>917663.99</v>
+        <v>500717.41</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>814913.85</v>
+        <v>436712.85</v>
       </c>
       <c r="E83" s="4" t="n">
         <v>252411.65</v>
@@ -6331,13 +6331,13 @@
         </is>
       </c>
       <c r="B84" s="18" t="n">
-        <v>-412877.25</v>
-      </c>
-      <c r="C84" s="18" t="n">
-        <v>-380489.55</v>
+        <v>-34368.21</v>
+      </c>
+      <c r="C84" s="13" t="n">
+        <v>36457.03</v>
       </c>
       <c r="D84" s="18" t="n">
-        <v>-399946.74</v>
+        <v>-21745.74</v>
       </c>
       <c r="E84" s="13" t="n">
         <v>177637.4</v>
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="B85" s="7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E85" s="7" t="n">
         <v>0</v>
@@ -6441,13 +6441,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>3533324.78</v>
+        <v>1640779.58</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>3853390.52</v>
+        <v>1768657.61</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>3273292.61</v>
+        <v>1382287.58</v>
       </c>
       <c r="E91" s="4" t="n">
         <v>564918.79</v>
@@ -6460,13 +6460,13 @@
         </is>
       </c>
       <c r="B92" s="13" t="n">
-        <v>3095419.79</v>
+        <v>1202874.59</v>
       </c>
       <c r="C92" s="13" t="n">
-        <v>3316216.08</v>
+        <v>1231483.17</v>
       </c>
       <c r="D92" s="13" t="n">
-        <v>2858325.5</v>
+        <v>967320.47</v>
       </c>
       <c r="E92" s="13" t="n">
         <v>134869.74</v>
@@ -6753,16 +6753,16 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>359.99</v>
+        <v>100.73</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>1799.94</v>
+        <v>503.67</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>7559.74</v>
+        <v>2115.43</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>53638.14</v>
+        <v>15009.47</v>
       </c>
     </row>
     <row r="7">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>1905854.19</v>
+        <v>13308.99</v>
       </c>
     </row>
     <row r="9">
@@ -6917,16 +6917,16 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>426</v>
+        <v>166.75</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>2130.02</v>
+        <v>833.76</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>8946.09</v>
+        <v>3501.78</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>63474.64</v>
+        <v>24845.98</v>
       </c>
     </row>
     <row r="19">
@@ -6936,7 +6936,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>1907333.87</v>
+        <v>14788.67</v>
       </c>
     </row>
     <row r="21">
@@ -7535,7 +7535,7 @@
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>-334389.75</v>
+        <v>-332849.58</v>
       </c>
     </row>
     <row r="6">
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>172831.32</v>
+        <v>171291.15</v>
       </c>
     </row>
     <row r="7">
@@ -9220,28 +9220,28 @@
         <v>1007201.77</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>3618935.84</v>
+        <v>1726390.64</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>808731.8100000001</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>4427667.65</v>
+        <v>2535122.45</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>2810204.03</v>
+        <v>917658.83</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>4.396</v>
+        <v>2.517</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>2.79</v>
+        <v>0.911</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>439.6</v>
+        <v>251.7</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>219.8</v>
+        <v>125.85</v>
       </c>
       <c r="K4" s="23" t="n">
         <v>14</v>
@@ -9294,28 +9294,28 @@
         <v>437904.99</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3533324.78</v>
+        <v>1640779.58</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>720586.41</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4253911.19</v>
+        <v>2361365.99</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2812738.37</v>
+        <v>920193.17</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>9.714</v>
+        <v>5.392</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>6.423</v>
+        <v>2.101</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>971.42</v>
+        <v>539.24</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>485.71</v>
+        <v>269.62</v>
       </c>
       <c r="K6" s="23" t="n">
         <v>13</v>
@@ -9356,7 +9356,7 @@
     <row r="3">
       <c r="A3" s="26" t="inlineStr">
         <is>
-          <t>HHI=0.1498  ·  effective N pairs=6.7  ·  max pair=29.52% of gross</t>
+          <t>HHI=0.075  ·  effective N pairs=13.3  ·  max pair=10.02% of gross</t>
         </is>
       </c>
     </row>
@@ -9395,20 +9395,20 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2102828</v>
+        <v>342668.34</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2102828</v>
+        <v>342668.34</v>
       </c>
       <c r="D6" s="27" t="n">
-        <v>208.78</v>
+        <v>34.02</v>
       </c>
       <c r="E6" s="27" t="n">
-        <v>47.49</v>
+        <v>13.52</v>
       </c>
       <c r="F6" s="23" t="n">
         <v>2</v>
@@ -9417,20 +9417,20 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>342668.34</v>
+        <v>269574</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>342668.34</v>
+        <v>269574</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>34.02</v>
+        <v>26.76</v>
       </c>
       <c r="E7" s="21" t="n">
-        <v>7.74</v>
+        <v>10.63</v>
       </c>
       <c r="F7" s="25" t="n">
         <v>2</v>
@@ -9439,20 +9439,20 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>269574</v>
+        <v>261427.36</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>269574</v>
+        <v>261427.36</v>
       </c>
       <c r="D8" s="27" t="n">
-        <v>26.76</v>
+        <v>25.96</v>
       </c>
       <c r="E8" s="27" t="n">
-        <v>6.09</v>
+        <v>10.31</v>
       </c>
       <c r="F8" s="23" t="n">
         <v>2</v>
@@ -9461,20 +9461,20 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>261427.36</v>
+        <v>221871.36</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>261427.36</v>
+        <v>221871.36</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>25.96</v>
+        <v>22.03</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>5.9</v>
+        <v>8.75</v>
       </c>
       <c r="F9" s="25" t="n">
         <v>2</v>
@@ -9483,20 +9483,20 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>221871.36</v>
+        <v>210282.8</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>221871.36</v>
+        <v>210282.8</v>
       </c>
       <c r="D10" s="27" t="n">
-        <v>22.03</v>
+        <v>20.88</v>
       </c>
       <c r="E10" s="27" t="n">
-        <v>5.01</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="F10" s="23" t="n">
         <v>2</v>
@@ -9518,7 +9518,7 @@
         <v>16.64</v>
       </c>
       <c r="E11" s="21" t="n">
-        <v>3.78</v>
+        <v>6.61</v>
       </c>
       <c r="F11" s="25" t="n">
         <v>1</v>
@@ -9540,7 +9540,7 @@
         <v>16.62</v>
       </c>
       <c r="E12" s="27" t="n">
-        <v>3.78</v>
+        <v>6.6</v>
       </c>
       <c r="F12" s="23" t="n">
         <v>2</v>
@@ -9562,7 +9562,7 @@
         <v>13.89</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>3.16</v>
+        <v>5.52</v>
       </c>
       <c r="F13" s="25" t="n">
         <v>2</v>
@@ -9584,7 +9584,7 @@
         <v>8.75</v>
       </c>
       <c r="E14" s="27" t="n">
-        <v>1.99</v>
+        <v>3.48</v>
       </c>
       <c r="F14" s="23" t="n">
         <v>1</v>
@@ -9606,7 +9606,7 @@
         <v>8.5</v>
       </c>
       <c r="E15" s="21" t="n">
-        <v>1.93</v>
+        <v>3.38</v>
       </c>
       <c r="F15" s="25" t="n">
         <v>1</v>
@@ -9653,16 +9653,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2753693.82</v>
+        <v>861148.62</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>73678.78</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2680015.04</v>
+        <v>787469.84</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>60.53</v>
+        <v>31.06</v>
       </c>
     </row>
     <row r="21">
@@ -9681,7 +9681,7 @@
         <v>-471861.66</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>-10.66</v>
+        <v>-18.61</v>
       </c>
     </row>
     <row r="22">
@@ -9700,7 +9700,7 @@
         <v>436962.62</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>9.869999999999999</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="23">
@@ -9719,7 +9719,7 @@
         <v>290507.22</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>6.56</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="24">
@@ -9738,7 +9738,7 @@
         <v>-76705.2</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>-1.73</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="25">
@@ -9757,7 +9757,7 @@
         <v>-48713.99</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>-1.1</v>
+        <v>-1.92</v>
       </c>
     </row>
   </sheetData>
@@ -9795,7 +9795,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>6.257</v>
+        <v>1.893</v>
       </c>
     </row>
     <row r="4">
@@ -9805,7 +9805,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>6.854</v>
+        <v>2.491</v>
       </c>
     </row>
     <row r="5">
@@ -9815,7 +9815,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>279.26</v>
+        <v>91.36</v>
       </c>
     </row>
     <row r="6">
@@ -9856,7 +9856,7 @@
         </is>
       </c>
       <c r="B10" s="27" t="n">
-        <v>60.53</v>
+        <v>31.06</v>
       </c>
     </row>
     <row r="11">
@@ -9866,7 +9866,7 @@
         </is>
       </c>
       <c r="B11" s="20" t="n">
-        <v>-10.66</v>
+        <v>-18.61</v>
       </c>
     </row>
     <row r="12">
@@ -9876,7 +9876,7 @@
         </is>
       </c>
       <c r="B12" s="27" t="n">
-        <v>9.869999999999999</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="13">
@@ -9886,7 +9886,7 @@
         </is>
       </c>
       <c r="B13" s="21" t="n">
-        <v>6.56</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="14">
@@ -9896,7 +9896,7 @@
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>-1.73</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="15">
@@ -9906,7 +9906,7 @@
         </is>
       </c>
       <c r="B15" s="20" t="n">
-        <v>-1.1</v>
+        <v>-1.92</v>
       </c>
     </row>
   </sheetData>
